--- a/spreadsheet/charles_stanley.xlsx
+++ b/spreadsheet/charles_stanley.xlsx
@@ -420,12 +420,12 @@
       </c>
     </row>
     <row r="2" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>7IM AAP Adventurous C Acc</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>GB00B2PB2C75</t>
         </is>
@@ -437,12 +437,12 @@
       </c>
     </row>
     <row r="3" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>7IM AAP Adventurous C Inc</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>GB00B2PB2B68</t>
         </is>
@@ -454,12 +454,12 @@
       </c>
     </row>
     <row r="4" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>7IM AAP Balanced C Acc</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>GB00B2PB3794</t>
         </is>
@@ -471,12 +471,12 @@
       </c>
     </row>
     <row r="5" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>7IM AAP Balanced C Inc</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>GB00B2PB2V64</t>
         </is>
@@ -488,12 +488,12 @@
       </c>
     </row>
     <row r="6" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>7IM AAP Cautious C Acc</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>GB00BMXV8544</t>
         </is>
@@ -505,12 +505,12 @@
       </c>
     </row>
     <row r="7" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>7IM AAP Cautious C Inc</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>GB00BMXV7D57</t>
         </is>
@@ -522,12 +522,12 @@
       </c>
     </row>
     <row r="8" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>7IM AAP Moderately Adventurous C Acc</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>GB00B2PB2M73</t>
         </is>
@@ -539,12 +539,12 @@
       </c>
     </row>
     <row r="9" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>7IM AAP Moderately Adventurous C Inc</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>GB00B2PB2K59</t>
         </is>
@@ -556,12 +556,12 @@
       </c>
     </row>
     <row r="10" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>7IM AAP Moderately Cautious C Acc</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>GB00B2PB2168</t>
         </is>
@@ -573,12 +573,12 @@
       </c>
     </row>
     <row r="11" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>7IM AAP Moderately Cautious C Inc</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>GB00B2PB2051</t>
         </is>
@@ -590,12 +590,12 @@
       </c>
     </row>
     <row r="12" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>7IM Adventurous C Acc</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>GB0033958009</t>
         </is>
@@ -607,12 +607,12 @@
       </c>
     </row>
     <row r="13" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>7IM Adventurous C Inc</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>GB0033957704</t>
         </is>
@@ -624,12 +624,12 @@
       </c>
     </row>
     <row r="14" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>7IM Balanced C Acc</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>GB0033959742</t>
         </is>
@@ -641,12 +641,12 @@
       </c>
     </row>
     <row r="15" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>7IM Balanced C Inc</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>GB0033959296</t>
         </is>
@@ -658,12 +658,12 @@
       </c>
     </row>
     <row r="16" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>7IM Moderately Adventurous C Acc</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>GB0033956516</t>
         </is>
@@ -675,12 +675,12 @@
       </c>
     </row>
     <row r="17" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>7IM Moderately Adventurous C Inc</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>GB0033956391</t>
         </is>
@@ -692,12 +692,12 @@
       </c>
     </row>
     <row r="18" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>7IM Moderately Cautious C Acc</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>GB0033953497</t>
         </is>
@@ -709,12 +709,12 @@
       </c>
     </row>
     <row r="19" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>7IM Moderately Cautious C Inc</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>GB0033953273</t>
         </is>
@@ -726,12 +726,12 @@
       </c>
     </row>
     <row r="20" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>7IM Pathbuilder 1 C Acc</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>GB00BMDPBQ86</t>
         </is>
@@ -743,12 +743,12 @@
       </c>
     </row>
     <row r="21" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>7IM Pathbuilder 1 C Inc</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>GB00BMDPC090</t>
         </is>
@@ -760,12 +760,12 @@
       </c>
     </row>
     <row r="22" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>7IM Pathbuilder 2 C Acc</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>GB00BMDPC322</t>
         </is>
@@ -777,12 +777,12 @@
       </c>
     </row>
     <row r="23" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>7IM Pathbuilder 2 C Inc</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>GB00BMDPC439</t>
         </is>
@@ -794,12 +794,12 @@
       </c>
     </row>
     <row r="24" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>7IM Pathbuilder 3 C Acc</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>GB00BMDPC769</t>
         </is>
@@ -811,12 +811,12 @@
       </c>
     </row>
     <row r="25" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>7IM Pathbuilder 3 C Inc</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>GB00BMDPC876</t>
         </is>
@@ -828,12 +828,12 @@
       </c>
     </row>
     <row r="26" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>7IM Pathbuilder 4 C Acc</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>GB00BMDPCC16</t>
         </is>
@@ -845,12 +845,12 @@
       </c>
     </row>
     <row r="27" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>7IM Pathbuilder 4 C Inc</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>GB00BMDPCD23</t>
         </is>
@@ -862,12 +862,12 @@
       </c>
     </row>
     <row r="28" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>AB American Growth Portfolio I GBP</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>LU1877329133</t>
         </is>
@@ -879,12 +879,12 @@
       </c>
     </row>
     <row r="29" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>AB Asia Ex Japan Equity Portfolio I GBP</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>LU1366339452</t>
         </is>
@@ -896,12 +896,12 @@
       </c>
     </row>
     <row r="30" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>AB China A Share Equity Portfolio I GBP</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>LU1979443402</t>
         </is>
@@ -913,12 +913,12 @@
       </c>
     </row>
     <row r="31" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>AB Concentrated US Equity Portfolio I GBP</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>LU1934454114</t>
         </is>
@@ -930,12 +930,12 @@
       </c>
     </row>
     <row r="32" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>AB Emerging Markets Multi Asset Portfolio ID H GBP</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>LU1514172565</t>
         </is>
@@ -947,12 +947,12 @@
       </c>
     </row>
     <row r="33" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>AB Emerging Markets Multi Asset Portfolio IH GBP</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>LU0633142699</t>
         </is>
@@ -964,12 +964,12 @@
       </c>
     </row>
     <row r="34" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>AB European Equity Portfolio I GBP</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>LU2037082463</t>
         </is>
@@ -981,12 +981,12 @@
       </c>
     </row>
     <row r="35" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>AB Global Core Equity Portfolio I USD</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>LU1061039506</t>
         </is>
@@ -998,12 +998,12 @@
       </c>
     </row>
     <row r="36" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>AB Global Dynamic Bond Portfolio I2 GBP</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>LU1005411068</t>
         </is>
@@ -1015,12 +1015,12 @@
       </c>
     </row>
     <row r="37" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>AB Global Growth Portfolio IX Acc GBP</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>LU1877329216</t>
         </is>
@@ -1032,12 +1032,12 @@
       </c>
     </row>
     <row r="38" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>AB Global Plus Fixed Income Portfolio I2H GBP</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>LU0683599889</t>
         </is>
@@ -1049,12 +1049,12 @@
       </c>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>AB International Health Care Portfolio I GBP</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>LU1934454544</t>
         </is>
@@ -1066,12 +1066,12 @@
       </c>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>AB International Health Care Portfolio I USD</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>LU0097089360</t>
         </is>
@@ -1083,12 +1083,12 @@
       </c>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>AB Low Volatility Equity Portfolio I H GBP</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>LU1306336170</t>
         </is>
@@ -1100,12 +1100,12 @@
       </c>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>AB RMB Income Plus Portfolio I2 GBP</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>LU0654558898</t>
         </is>
@@ -1117,12 +1117,12 @@
       </c>
     </row>
     <row r="43" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>AB SICAV I - Sustainable Global Thematic Portfolio I USD</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>LU0069063542</t>
         </is>
@@ -1134,12 +1134,12 @@
       </c>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>AB Select Absolute Alpha Portfolio IH GBP</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>LU0736560284</t>
         </is>
@@ -1151,12 +1151,12 @@
       </c>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>AB Select US Equity Portfolio I USD</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>LU0683600992</t>
         </is>
@@ -1168,12 +1168,12 @@
       </c>
     </row>
     <row r="46" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>AB Select US Equity Portfolio IH GBP</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>LU0683601297</t>
         </is>
@@ -1185,12 +1185,12 @@
       </c>
     </row>
     <row r="47" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>AB Short Duration High Yield Portfolio I2H GBP</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>LU0654560795</t>
         </is>
@@ -1202,12 +1202,12 @@
       </c>
     </row>
     <row r="48" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>AB Short Duration High Yield Portfolio ITH GBP</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>LU1306335958</t>
         </is>
@@ -1219,12 +1219,12 @@
       </c>
     </row>
     <row r="49" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>AB Sustainable Euro High Yield Portfolio I2H GBP</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>LU1207091197</t>
         </is>
@@ -1236,12 +1236,12 @@
       </c>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>AB US Low Volatility Equity Portfolio I Acc GBP</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>LU2339504834</t>
         </is>
@@ -1253,12 +1253,12 @@
       </c>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>AB US Low Volatility Equity Portfolio I Acc USD</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>LU2339504248</t>
         </is>
@@ -1270,12 +1270,12 @@
       </c>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>AXA Framlington UK Smaller Companies Z Acc</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>GB00B7MMLM18</t>
         </is>
@@ -1287,12 +1287,12 @@
       </c>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>AXA Framlington UK Smaller Companies Z Inc</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>GB00BRJZVS95</t>
         </is>
@@ -1304,12 +1304,12 @@
       </c>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>AXA Global Distribution Z Acc</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>GB0008309063</t>
         </is>
@@ -1321,12 +1321,12 @@
       </c>
     </row>
     <row r="55" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>AXA Global Distribution Z Inc</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>GB0008308982</t>
         </is>
@@ -1338,12 +1338,12 @@
       </c>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>AXA Global High Yield Z Gr Acc</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>GB00B29NGF01</t>
         </is>
@@ -1355,12 +1355,12 @@
       </c>
     </row>
     <row r="57" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>AXA Global High Yield Z Gr Inc</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>GB00B29NG940</t>
         </is>
@@ -1372,12 +1372,12 @@
       </c>
     </row>
     <row r="58" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>AXA Global Short Duration Bonds Z Acc</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>GB00BDFZQV30</t>
         </is>
@@ -1389,12 +1389,12 @@
       </c>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>AXA Global Short Duration Bonds Z Inc</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>GB00BDFZQW47</t>
         </is>
@@ -1406,12 +1406,12 @@
       </c>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>AXA Global Strategic Bond Z Acc Quarterly GBP</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>GB00BMZCH470</t>
         </is>
@@ -1423,12 +1423,12 @@
       </c>
     </row>
     <row r="61" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>AXA Global Strategic Bond Z Inc Quarterly GBP</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>GB00BMZCH363</t>
         </is>
@@ -1440,12 +1440,12 @@
       </c>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>AXA Global Sustainable Managed Z Acc</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>GB00B7MMHK16</t>
         </is>
@@ -1457,12 +1457,12 @@
       </c>
     </row>
     <row r="63" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>AXA Global Sustainable Managed Z Inc</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>GB00B7MQY793</t>
         </is>
@@ -1474,12 +1474,12 @@
       </c>
     </row>
     <row r="64" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>AXA Green Short Duration Bond Z Acc</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>GB00BNNDLG95</t>
         </is>
@@ -1491,12 +1491,12 @@
       </c>
     </row>
     <row r="65" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>AXA Green Short Duration Bond Z Inc</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>GB00BNNDLH03</t>
         </is>
@@ -1508,12 +1508,12 @@
       </c>
     </row>
     <row r="66" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>AXA Lifetime Distribution Z Acc</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>GB00BYVDW547</t>
         </is>
@@ -1525,12 +1525,12 @@
       </c>
     </row>
     <row r="67" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>AXA Lifetime Distribution Z Inc</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>GB00BYVDW653</t>
         </is>
@@ -1542,12 +1542,12 @@
       </c>
     </row>
     <row r="68" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>AXA Managed Income Z Gross Acc</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>GB00B7H1PG56</t>
         </is>
@@ -1559,12 +1559,12 @@
       </c>
     </row>
     <row r="69" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>AXA Managed Income Z Gross Inc</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>GB00B71DB365</t>
         </is>
@@ -1576,12 +1576,12 @@
       </c>
     </row>
     <row r="70" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>AXA People &amp; Planet Equity S Acc GBP</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>GB00BMGMLQ68</t>
         </is>
@@ -1593,12 +1593,12 @@
       </c>
     </row>
     <row r="71" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>AXA People &amp; Planet Equity S Inc GBP</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>GB00BMGMLP51</t>
         </is>
@@ -1610,12 +1610,12 @@
       </c>
     </row>
     <row r="72" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>AXA People &amp; Planet Equity Z Acc</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>GB00B4490M25</t>
         </is>
@@ -1627,12 +1627,12 @@
       </c>
     </row>
     <row r="73" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>AXA People &amp; Planet Equity Z Inc</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>GB00B403RF05</t>
         </is>
@@ -1644,12 +1644,12 @@
       </c>
     </row>
     <row r="74" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>AXA Sterling Corporate Bond R Gr Acc</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>GB00B0T9V821</t>
         </is>
@@ -1661,12 +1661,12 @@
       </c>
     </row>
     <row r="75" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>AXA Sterling Corporate Bond R Gr Inc</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>GB00B0T9V938</t>
         </is>
@@ -1678,12 +1678,12 @@
       </c>
     </row>
     <row r="76" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>AXA Sterling Credit Short Duration Bond Z Gr Acc</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>GB00B5L2N222</t>
         </is>
@@ -1695,12 +1695,12 @@
       </c>
     </row>
     <row r="77" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>AXA Sterling Credit Short Duration Bond Z Gr Inc</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>GB00B5VL0B78</t>
         </is>
@@ -1712,12 +1712,12 @@
       </c>
     </row>
     <row r="78" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>AXA UK Sustainable Equity Z Acc</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>GB00B51R1233</t>
         </is>
@@ -1729,12 +1729,12 @@
       </c>
     </row>
     <row r="79" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>AXA UK Sustainable Equity Z Inc</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>GB00B55S4R83</t>
         </is>
@@ -1746,12 +1746,12 @@
       </c>
     </row>
     <row r="80" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>AXA US Short Duration High Yield Bond ZI Gr Acc</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>GB00B5WM6Y48</t>
         </is>
@@ -1763,12 +1763,12 @@
       </c>
     </row>
     <row r="81" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>AXA US Short Duration High Yield Bond ZI Gr Inc</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>GB00B5T0SW38</t>
         </is>
@@ -1780,12 +1780,12 @@
       </c>
     </row>
     <row r="82" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>AXA World Funds - Clean Energy F Hedged Cap GBP</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>LU1914342933</t>
         </is>
@@ -1797,12 +1797,12 @@
       </c>
     </row>
     <row r="83" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>AXA World Funds - Digital Economy F Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>LU1694772135</t>
         </is>
@@ -1814,12 +1814,12 @@
       </c>
     </row>
     <row r="84" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>AXA World Funds - Global Inflation Bonds F Hedged Cap GBP</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>LU1002649512</t>
         </is>
@@ -1831,12 +1831,12 @@
       </c>
     </row>
     <row r="85" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>AXA World Funds - Global Strategic Income F Hedged Cap GBP</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>LU0746605764</t>
         </is>
@@ -1848,12 +1848,12 @@
       </c>
     </row>
     <row r="86" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>AXA World Funds - Sustainable Equity QI F Cap EUR</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>LU1774150145</t>
         </is>
@@ -1865,12 +1865,12 @@
       </c>
     </row>
     <row r="87" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>AXA World Funds - UK Equity F Cap GBP</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>LU1319653462</t>
         </is>
@@ -1882,12 +1882,12 @@
       </c>
     </row>
     <row r="88" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>AXA World Funds - UK Equity I Cap GBP</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>LU1319653892</t>
         </is>
@@ -1899,12 +1899,12 @@
       </c>
     </row>
     <row r="89" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>BA Beutel Goodman US Value Class SI Unhedged Acc GBP</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>IE00BN940L42</t>
         </is>
@@ -1916,12 +1916,12 @@
       </c>
     </row>
     <row r="90" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>BA Beutel Goodman US Value Class SI Unhedged Dis GBP</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>IE00BN940M58</t>
         </is>
@@ -1933,12 +1933,12 @@
       </c>
     </row>
     <row r="91" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon Multi-Asset Moderate Institutional Shares W Acc GBP</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>GB00BRJTS680</t>
         </is>
@@ -1950,12 +1950,12 @@
       </c>
     </row>
     <row r="92" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon Real Return (Responsible) Inst W Acc</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>GB00BD6DRD55</t>
         </is>
@@ -1967,12 +1967,12 @@
       </c>
     </row>
     <row r="93" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon Real Return (Responsible) Inst W Inc</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>GB00BD6DRF79</t>
         </is>
@@ -1984,12 +1984,12 @@
       </c>
     </row>
     <row r="94" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon Real Return Inst W Acc</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>GB00B8GG4B61</t>
         </is>
@@ -2001,12 +2001,12 @@
       </c>
     </row>
     <row r="95" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon Real Return Inst W Inc</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>GB00B7W36529</t>
         </is>
@@ -2018,12 +2018,12 @@
       </c>
     </row>
     <row r="96" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon Responsible Horizons UK Corporate Bond Inst W Acc GBP</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>GB00B8KDLX41</t>
         </is>
@@ -2035,12 +2035,12 @@
       </c>
     </row>
     <row r="97" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon Responsible Horizons UK Corporate Bond Inst W Inc GBP</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>GB00B8KCZN97</t>
         </is>
@@ -2052,12 +2052,12 @@
       </c>
     </row>
     <row r="98" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon Sustainable Global Dynamic Bond W Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>IE00BFZMJ537</t>
         </is>
@@ -2069,12 +2069,12 @@
       </c>
     </row>
     <row r="99" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon Sustainable Global Dynamic Bond W Hedged Inc GBP</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>IE00BFZMJ644</t>
         </is>
@@ -2086,12 +2086,12 @@
       </c>
     </row>
     <row r="100" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon UK Equity Inst W Acc</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>GB00B6X4W596</t>
         </is>
@@ -2103,12 +2103,12 @@
       </c>
     </row>
     <row r="101" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon UK Equity Inst W Inc</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>GB00B8GHL294</t>
         </is>
@@ -2120,12 +2120,12 @@
       </c>
     </row>
     <row r="102" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon UK Income Inst W Acc</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>GB00B7M90R07</t>
         </is>
@@ -2137,12 +2137,12 @@
       </c>
     </row>
     <row r="103" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon UK Income Inst W Inc</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>GB00B7W2G379</t>
         </is>
@@ -2154,12 +2154,12 @@
       </c>
     </row>
     <row r="104" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon US Equity Income Fund W Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>IE00BD7Y0G10</t>
         </is>
@@ -2171,12 +2171,12 @@
       </c>
     </row>
     <row r="105" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon US Equity Income Fund W Inc GBP</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>IE00BD5M7551</t>
         </is>
@@ -2188,12 +2188,12 @@
       </c>
     </row>
     <row r="106" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon US Equity Income Inst W Acc</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>GB00BGV53H32</t>
         </is>
@@ -2205,12 +2205,12 @@
       </c>
     </row>
     <row r="107" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>BNY Mellon US Equity Income Inst W Inc</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>GB00BGV53J55</t>
         </is>
@@ -2222,12 +2222,12 @@
       </c>
     </row>
     <row r="108" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>BNY Multi-Sector Credit Income W Hedged</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>IE00BYRCJS78</t>
         </is>
@@ -2239,12 +2239,12 @@
       </c>
     </row>
     <row r="109" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>BNY Strategic Bond F Inc</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>GB00BMD53170</t>
         </is>
@@ -2256,12 +2256,12 @@
       </c>
     </row>
     <row r="110" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>BNY Strategic Bond Inst W Acc</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>GB00BMD53287</t>
         </is>
@@ -2273,12 +2273,12 @@
       </c>
     </row>
     <row r="111" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>BNY Strategic Bond Inst W Inc</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>GB00BMD53394</t>
         </is>
@@ -2290,12 +2290,12 @@
       </c>
     </row>
     <row r="112" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>Baillie Gifford American B Acc</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>GB0006061963</t>
         </is>
@@ -2307,12 +2307,12 @@
       </c>
     </row>
     <row r="113" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>Baillie Gifford American B Inc</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>GB0006061856</t>
         </is>
@@ -2324,12 +2324,12 @@
       </c>
     </row>
     <row r="114" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>Baillie Gifford Cautious Managed B ACC GBP</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>GB00BV0V1394</t>
         </is>
@@ -2341,12 +2341,12 @@
       </c>
     </row>
     <row r="115" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>Baillie Gifford Cautious Managed B DST GBP</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>GB00BV0V1402</t>
         </is>
@@ -2358,12 +2358,12 @@
       </c>
     </row>
     <row r="116" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>Baillie Gifford China B Acc</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>GB00B39RMM81</t>
         </is>
@@ -2375,12 +2375,12 @@
       </c>
     </row>
     <row r="117" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>Baillie Gifford China B Inc</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>GB00B3K73F73</t>
         </is>
@@ -2392,12 +2392,12 @@
       </c>
     </row>
     <row r="118" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>Baillie Gifford Developed Asia Pacific B Acc</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>GB0030492044</t>
         </is>
@@ -2409,12 +2409,12 @@
       </c>
     </row>
     <row r="119" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>Baillie Gifford Developed Asia Pacific B Inc</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>GB0030491632</t>
         </is>
@@ -2426,12 +2426,12 @@
       </c>
     </row>
     <row r="120" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="6" t="inlineStr">
         <is>
           <t>Baillie Gifford Emerging Markets Growth B Acc</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>GB0006020647</t>
         </is>
@@ -2443,12 +2443,12 @@
       </c>
     </row>
     <row r="121" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>Baillie Gifford Emerging Markets Growth B Inc</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>GB0006020530</t>
         </is>
@@ -2460,12 +2460,12 @@
       </c>
     </row>
     <row r="122" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="6" t="inlineStr">
         <is>
           <t>Baillie Gifford Emerging Markets Leading Companies B Acc GBP</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>GB00B06HZN29</t>
         </is>
@@ -2477,12 +2477,12 @@
       </c>
     </row>
     <row r="123" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>Brandes European Value I GBP</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>IE0031575057</t>
         </is>
@@ -2494,12 +2494,12 @@
       </c>
     </row>
     <row r="124" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="6" t="inlineStr">
         <is>
           <t>Brandes European Value I1 GBP</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="6" t="inlineStr">
         <is>
           <t>IE00BYXWTN61</t>
         </is>
@@ -2511,12 +2511,12 @@
       </c>
     </row>
     <row r="125" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="6" t="inlineStr">
         <is>
           <t>Brandes Global Value I GBP</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="6" t="inlineStr">
         <is>
           <t>IE0031574423</t>
         </is>
@@ -2528,12 +2528,12 @@
       </c>
     </row>
     <row r="126" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="6" t="inlineStr">
         <is>
           <t>Brandes Global Value I1 GBP</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="6" t="inlineStr">
         <is>
           <t>IE00B1SHJJ14</t>
         </is>
@@ -2545,12 +2545,12 @@
       </c>
     </row>
     <row r="127" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>Brandes US Value I</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>IE0031575610</t>
         </is>
@@ -2562,12 +2562,12 @@
       </c>
     </row>
     <row r="128" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="6" t="inlineStr">
         <is>
           <t>Brevan Howard Absolute Return Government Bond A Acc GBP</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>LU1917107465</t>
         </is>
@@ -2579,12 +2579,12 @@
       </c>
     </row>
     <row r="129" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>Brevan Howard Absolute Return Government Bond A Dis GBP</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>LU2360066034</t>
         </is>
@@ -2596,12 +2596,12 @@
       </c>
     </row>
     <row r="130" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>Brevan Howard Absolute Return Government Bond A2 Acc GBP</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>LU2428337914</t>
         </is>
@@ -2613,12 +2613,12 @@
       </c>
     </row>
     <row r="131" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>Brevan Howard Absolute Return Government Bond A2 Dis GBP</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>LU2428337245</t>
         </is>
@@ -2630,12 +2630,12 @@
       </c>
     </row>
     <row r="132" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>Brevan Howard Absolute Return Government Bond A2m Acc GBP</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>LU2428334499</t>
         </is>
@@ -2647,12 +2647,12 @@
       </c>
     </row>
     <row r="133" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>Brevan Howard Absolute Return Government Bond A2m Dis GBP</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>LU2428338565</t>
         </is>
@@ -2664,12 +2664,12 @@
       </c>
     </row>
     <row r="134" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>Brevan Howard Absolute Return Government Bond A3 Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>LU2830332958</t>
         </is>
@@ -2681,12 +2681,12 @@
       </c>
     </row>
     <row r="135" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="6" t="inlineStr">
         <is>
           <t>Brevan Howard Absolute Return Government Bond A3 Inc GBP</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>LU2663018120</t>
         </is>
@@ -2698,12 +2698,12 @@
       </c>
     </row>
     <row r="136" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="6" t="inlineStr">
         <is>
           <t>Brevan Howard Absolute Return Government Bond Am GBP</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>LU1917107549</t>
         </is>
@@ -2715,12 +2715,12 @@
       </c>
     </row>
     <row r="137" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>Bridge Iridian U.S. Corporate Change Equity IP Dis GBP</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>IE000W5PNBW3</t>
         </is>
@@ -2732,12 +2732,12 @@
       </c>
     </row>
     <row r="138" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory Global Leaders B Acc GBP</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B138" s="6" t="inlineStr">
         <is>
           <t>IE00BD9MKL82</t>
         </is>
@@ -2749,12 +2749,12 @@
       </c>
     </row>
     <row r="139" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory Global Leaders B Dis GBP</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B139" s="6" t="inlineStr">
         <is>
           <t>IE00BYPJ0V09</t>
         </is>
@@ -2766,12 +2766,12 @@
       </c>
     </row>
     <row r="140" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory Global Leaders BH Acc GBP</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B140" s="6" t="inlineStr">
         <is>
           <t>IE00BVVHP902</t>
         </is>
@@ -2783,12 +2783,12 @@
       </c>
     </row>
     <row r="141" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory Global Leaders SI Dis USD</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B141" s="6" t="inlineStr">
         <is>
           <t>IE00BG0R3B42</t>
         </is>
@@ -2800,12 +2800,12 @@
       </c>
     </row>
     <row r="142" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory Global Leaders Sustainable B Acc GBP</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B142" s="6" t="inlineStr">
         <is>
           <t>IE00BJXBP856</t>
         </is>
@@ -2817,12 +2817,12 @@
       </c>
     </row>
     <row r="143" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory Global Sustainable Total Return Bond (GBP) Sterling Class B Acc GBP</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" s="6" t="inlineStr">
         <is>
           <t>IE000E587MY6</t>
         </is>
@@ -2834,12 +2834,12 @@
       </c>
     </row>
     <row r="144" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory Global Sustainable Total Return Bond (GBP) Sterling Class B Dis GBP</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B144" s="6" t="inlineStr">
         <is>
           <t>IE000V34XHS4</t>
         </is>
@@ -2851,12 +2851,12 @@
       </c>
     </row>
     <row r="145" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory US Equity Growth B H GBP</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B145" s="6" t="inlineStr">
         <is>
           <t>IE00B4MHR723</t>
         </is>
@@ -2868,12 +2868,12 @@
       </c>
     </row>
     <row r="146" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory US Flexible Equity B Hedged Dis GBP</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>IE00BYPJ0M18</t>
         </is>
@@ -2885,12 +2885,12 @@
       </c>
     </row>
     <row r="147" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory US Flexible Equity B Hedged GBP</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B147" s="6" t="inlineStr">
         <is>
           <t>IE00BJ357W50</t>
         </is>
@@ -2902,12 +2902,12 @@
       </c>
     </row>
     <row r="148" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory US Flexible Equity C Dis GBP</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>IE00BYPJ0L01</t>
         </is>
@@ -2919,12 +2919,12 @@
       </c>
     </row>
     <row r="149" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory US Flexible Equity M Dis GBP</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B149" s="6" t="inlineStr">
         <is>
           <t>IE00BYT42828</t>
         </is>
@@ -2936,12 +2936,12 @@
       </c>
     </row>
     <row r="150" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory US Mid-Cap Growth B Acc GBP</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B150" s="6" t="inlineStr">
         <is>
           <t>IE00BYW8R751</t>
         </is>
@@ -2953,12 +2953,12 @@
       </c>
     </row>
     <row r="151" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="6" t="inlineStr">
         <is>
           <t>Brown Advisory US Mid-Cap Growth Class B H GBP Acc</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B151" s="6" t="inlineStr">
         <is>
           <t>IE00BYW8R868</t>
         </is>
@@ -2970,12 +2970,12 @@
       </c>
     </row>
     <row r="152" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="6" t="inlineStr">
         <is>
           <t>Evelyn Cautious Portfolio Clean Inc</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B152" s="6" t="inlineStr">
         <is>
           <t>IE00BYX8LF00</t>
         </is>
@@ -2987,12 +2987,12 @@
       </c>
     </row>
     <row r="153" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="6" t="inlineStr">
         <is>
           <t>Evelyn Conservative Portfolio Clean Acc GBP</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B153" s="6" t="inlineStr">
         <is>
           <t>IE00BFY1MG36</t>
         </is>
@@ -3004,12 +3004,12 @@
       </c>
     </row>
     <row r="154" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="6" t="inlineStr">
         <is>
           <t>Evelyn Conservative Portfolio Clean Dist GBP</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B154" s="6" t="inlineStr">
         <is>
           <t>IE00BFY1MH43</t>
         </is>
@@ -3021,12 +3021,12 @@
       </c>
     </row>
     <row r="155" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="6" t="inlineStr">
         <is>
           <t>Evelyn Defensive Growth Fund K Dist GBP</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B155" s="6" t="inlineStr">
         <is>
           <t>IE000QAQGPJ6</t>
         </is>
@@ -3038,12 +3038,12 @@
       </c>
     </row>
     <row r="156" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="6" t="inlineStr">
         <is>
           <t>Evelyn Defensive Portfolio Clean Acc</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B156" s="6" t="inlineStr">
         <is>
           <t>IE00BYX8KL94</t>
         </is>
@@ -3055,12 +3055,12 @@
       </c>
     </row>
     <row r="157" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="6" t="inlineStr">
         <is>
           <t>Evelyn Defensive Portfolio Clean Inc</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B157" s="6" t="inlineStr">
         <is>
           <t>IE00BYX8KM02</t>
         </is>
@@ -3072,12 +3072,12 @@
       </c>
     </row>
     <row r="158" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="6" t="inlineStr">
         <is>
           <t>Evelyn Growth Portfolio Clean Acc</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B158" s="6" t="inlineStr">
         <is>
           <t>IE00BYX8KR56</t>
         </is>
@@ -3089,12 +3089,12 @@
       </c>
     </row>
     <row r="159" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="6" t="inlineStr">
         <is>
           <t>Evelyn Growth Portfolio Clean Inc</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>IE00BYX8KS63</t>
         </is>
@@ -3106,12 +3106,12 @@
       </c>
     </row>
     <row r="160" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="6" t="inlineStr">
         <is>
           <t>Evelyn Horizon Cautious Portfolio Clean Acc</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B160" s="6" t="inlineStr">
         <is>
           <t>IE00BYX8L381</t>
         </is>
@@ -3123,12 +3123,12 @@
       </c>
     </row>
     <row r="161" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="6" t="inlineStr">
         <is>
           <t>Evelyn Horizon Cautious Portfolio Clean Inc</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B161" s="6" t="inlineStr">
         <is>
           <t>IE00BYX8L498</t>
         </is>
@@ -3140,12 +3140,12 @@
       </c>
     </row>
     <row r="162" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="6" t="inlineStr">
         <is>
           <t>Evelyn Income Portfolio Clean Acc GBP</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B162" s="6" t="inlineStr">
         <is>
           <t>IE00BFY1N269</t>
         </is>
@@ -3157,12 +3157,12 @@
       </c>
     </row>
     <row r="163" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="6" t="inlineStr">
         <is>
           <t>Evelyn Income Portfolio Clean Dist GBP</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>IE00BFY1N376</t>
         </is>
@@ -3174,12 +3174,12 @@
       </c>
     </row>
     <row r="164" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="6" t="inlineStr">
         <is>
           <t>Evelyn MM Endurance Balanced B Inc</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B164" s="6" t="inlineStr">
         <is>
           <t>GB00B43LJX34</t>
         </is>
@@ -3191,12 +3191,12 @@
       </c>
     </row>
     <row r="165" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A165" t="inlineStr">
+      <c r="A165" s="6" t="inlineStr">
         <is>
           <t>Evelyn MM Global Investment B Inc</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B165" s="6" t="inlineStr">
         <is>
           <t>GB00B89C3K35</t>
         </is>
@@ -3208,12 +3208,12 @@
       </c>
     </row>
     <row r="166" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A166" t="inlineStr">
+      <c r="A166" s="6" t="inlineStr">
         <is>
           <t>Evelyn Maximum Growth Portfolio Clean Acc GBP</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B166" s="6" t="inlineStr">
         <is>
           <t>IE00BFY1PL93</t>
         </is>
@@ -3225,12 +3225,12 @@
       </c>
     </row>
     <row r="167" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A167" t="inlineStr">
+      <c r="A167" s="6" t="inlineStr">
         <is>
           <t>Evelyn Maximum Growth Portfolio Clean Dist GBP</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B167" s="6" t="inlineStr">
         <is>
           <t>IE00BFY1PM01</t>
         </is>
@@ -3242,12 +3242,12 @@
       </c>
     </row>
     <row r="168" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="6" t="inlineStr">
         <is>
           <t>Evelyn Multi-Asset Adventurous Clean Acc</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B168" s="6" t="inlineStr">
         <is>
           <t>IE0005BN6N99</t>
         </is>
@@ -3259,12 +3259,12 @@
       </c>
     </row>
     <row r="169" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A169" t="inlineStr">
+      <c r="A169" s="6" t="inlineStr">
         <is>
           <t>Evelyn Multi-Asset Adventurous Clean Dis</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B169" s="6" t="inlineStr">
         <is>
           <t>IE0009YPXMY4</t>
         </is>
@@ -3276,12 +3276,12 @@
       </c>
     </row>
     <row r="170" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="6" t="inlineStr">
         <is>
           <t>Evelyn Multi-Asset Balanced Clean Acc</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B170" s="6" t="inlineStr">
         <is>
           <t>IE000DZC6LL2</t>
         </is>
@@ -3293,12 +3293,12 @@
       </c>
     </row>
     <row r="171" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="6" t="inlineStr">
         <is>
           <t>Evelyn Multi-Asset Balanced Clean Dis</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B171" s="6" t="inlineStr">
         <is>
           <t>IE000U6RZLZ5</t>
         </is>
@@ -3310,12 +3310,12 @@
       </c>
     </row>
     <row r="172" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="6" t="inlineStr">
         <is>
           <t>Evelyn Multi-Asset Growth Clean Acc</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B172" s="6" t="inlineStr">
         <is>
           <t>IE000LIIQTD1</t>
         </is>
@@ -3327,12 +3327,12 @@
       </c>
     </row>
     <row r="173" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A173" t="inlineStr">
+      <c r="A173" s="6" t="inlineStr">
         <is>
           <t>Evelyn Multi-Asset Growth Clean Dis</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B173" s="6" t="inlineStr">
         <is>
           <t>IE0007957L14</t>
         </is>
@@ -3344,12 +3344,12 @@
       </c>
     </row>
     <row r="174" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="6" t="inlineStr">
         <is>
           <t>Evelyn Multi-Asset Maximum Growth Clean Acc</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B174" s="6" t="inlineStr">
         <is>
           <t>IE0001GNZK29</t>
         </is>
@@ -3361,12 +3361,12 @@
       </c>
     </row>
     <row r="175" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="6" t="inlineStr">
         <is>
           <t>Evelyn Multi-Asset Maximum Growth Clean Dis</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B175" s="6" t="inlineStr">
         <is>
           <t>IE000A1XXDS5</t>
         </is>
@@ -3378,12 +3378,12 @@
       </c>
     </row>
     <row r="176" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Asia ex-Japan Equity F Acc GBP</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B176" s="6" t="inlineStr">
         <is>
           <t>IE00B8449Z10</t>
         </is>
@@ -3395,12 +3395,12 @@
       </c>
     </row>
     <row r="177" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Asia ex-Japan Equity F2 Dis GBP</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B177" s="6" t="inlineStr">
         <is>
           <t>IE00B84WGD25</t>
         </is>
@@ -3412,12 +3412,12 @@
       </c>
     </row>
     <row r="178" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global Emerging Markets Equity F2 Hedged Inc GBP</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B178" s="6" t="inlineStr">
         <is>
           <t>IE00BBHXD658</t>
         </is>
@@ -3429,12 +3429,12 @@
       </c>
     </row>
     <row r="179" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A179" t="inlineStr">
+      <c r="A179" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global Emerging Markets Equity L Acc GBP</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B179" s="6" t="inlineStr">
         <is>
           <t>IE00BZ4C8688</t>
         </is>
@@ -3446,12 +3446,12 @@
       </c>
     </row>
     <row r="180" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A180" t="inlineStr">
+      <c r="A180" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global Emerging Markets Equity L2 Inc GBP</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B180" s="6" t="inlineStr">
         <is>
           <t>IE00BZ4C8795</t>
         </is>
@@ -3463,12 +3463,12 @@
       </c>
     </row>
     <row r="181" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global Equity ESG Pathway F Acc GBP</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B181" s="6" t="inlineStr">
         <is>
           <t>IE00BKRCPS19</t>
         </is>
@@ -3480,12 +3480,12 @@
       </c>
     </row>
     <row r="182" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global Equity ESG Pathway F2 Portfolio Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B182" s="6" t="inlineStr">
         <is>
           <t>IE00BFZWQ523</t>
         </is>
@@ -3497,12 +3497,12 @@
       </c>
     </row>
     <row r="183" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global High Yield Credit Engagement F Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B183" s="6" t="inlineStr">
         <is>
           <t>IE00BK0X9Q74</t>
         </is>
@@ -3514,12 +3514,12 @@
       </c>
     </row>
     <row r="184" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global High Yield Credit Engagement F Unhedged Acc USD</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B184" s="6" t="inlineStr">
         <is>
           <t>IE00BK0X9R81</t>
         </is>
@@ -3531,12 +3531,12 @@
       </c>
     </row>
     <row r="185" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global High Yield Credit Engagement M2 Hedged Dis GBP</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B185" s="6" t="inlineStr">
         <is>
           <t>IE00BLPJRX06</t>
         </is>
@@ -3548,12 +3548,12 @@
       </c>
     </row>
     <row r="186" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global High Yield Credit F Acc GBP</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B186" s="6" t="inlineStr">
         <is>
           <t>IE00B4W78028</t>
         </is>
@@ -3565,12 +3565,12 @@
       </c>
     </row>
     <row r="187" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global High Yield Credit F Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B187" s="6" t="inlineStr">
         <is>
           <t>IE00BBJPFN04</t>
         </is>
@@ -3582,12 +3582,12 @@
       </c>
     </row>
     <row r="188" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A188" t="inlineStr">
+      <c r="A188" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global High Yield Credit F2 Hedged Inc GBP</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>IE00BBJPFM96</t>
         </is>
@@ -3599,12 +3599,12 @@
       </c>
     </row>
     <row r="189" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A189" t="inlineStr">
+      <c r="A189" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global SMID Equity Engagement F Acc GBP</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B189" s="6" t="inlineStr">
         <is>
           <t>IE00BD3FN141</t>
         </is>
@@ -3616,12 +3616,12 @@
       </c>
     </row>
     <row r="190" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global SMID Equity Engagement F Portfolio Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>IE00BFZWQ416</t>
         </is>
@@ -3633,12 +3633,12 @@
       </c>
     </row>
     <row r="191" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global SMID Equity Engagement X Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B191" s="6" t="inlineStr">
         <is>
           <t>IE00BD3FN695</t>
         </is>
@@ -3650,12 +3650,12 @@
       </c>
     </row>
     <row r="192" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global Small Cap Equity F Acc GBP</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B192" s="6" t="inlineStr">
         <is>
           <t>IE00BVVB5N62</t>
         </is>
@@ -3667,12 +3667,12 @@
       </c>
     </row>
     <row r="193" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A193" t="inlineStr">
+      <c r="A193" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Global Small Cap Equity F Inc GBP</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B193" s="6" t="inlineStr">
         <is>
           <t>IE00BVVB5X60</t>
         </is>
@@ -3684,12 +3684,12 @@
       </c>
     </row>
     <row r="194" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Sustainable Global Equity X Acc GBP</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B194" s="6" t="inlineStr">
         <is>
           <t>IE00BNKVQP04</t>
         </is>
@@ -3701,12 +3701,12 @@
       </c>
     </row>
     <row r="195" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes US SMID Equity F Acc GBP</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B195" s="6" t="inlineStr">
         <is>
           <t>IE00B8JBCY79</t>
         </is>
@@ -3718,12 +3718,12 @@
       </c>
     </row>
     <row r="196" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes US SMID Equity F Dis GBP</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B196" s="6" t="inlineStr">
         <is>
           <t>IE00B8493D29</t>
         </is>
@@ -3735,12 +3735,12 @@
       </c>
     </row>
     <row r="197" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes US SMID Equity F Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B197" s="6" t="inlineStr">
         <is>
           <t>IE00BBL4VC65</t>
         </is>
@@ -3752,12 +3752,12 @@
       </c>
     </row>
     <row r="198" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes US SMID Equity F2 Hedged Inc GBP</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B198" s="6" t="inlineStr">
         <is>
           <t>IE00BBL4VB58</t>
         </is>
@@ -3769,12 +3769,12 @@
       </c>
     </row>
     <row r="199" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A199" t="inlineStr">
+      <c r="A199" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Unconstrained Credit F Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B199" s="6" t="inlineStr">
         <is>
           <t>IE00BFB40T42</t>
         </is>
@@ -3786,12 +3786,12 @@
       </c>
     </row>
     <row r="200" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A200" t="inlineStr">
+      <c r="A200" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Unconstrained Credit L2 Dis GBP</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B200" s="6" t="inlineStr">
         <is>
           <t>IE000P0WY2X0</t>
         </is>
@@ -3803,12 +3803,12 @@
       </c>
     </row>
     <row r="201" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="6" t="inlineStr">
         <is>
           <t>Federated Hermes Unconstrained Credit L2 Hedged Dis GBP</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B201" s="6" t="inlineStr">
         <is>
           <t>IE000ZUCAJ90</t>
         </is>
@@ -3820,12 +3820,12 @@
       </c>
     </row>
     <row r="202" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="6" t="inlineStr">
         <is>
           <t>GS Green Bond I (hedged i) Cap GBP</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B202" s="6" t="inlineStr">
         <is>
           <t>LU2213813608</t>
         </is>
@@ -3837,12 +3837,12 @@
       </c>
     </row>
     <row r="203" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A203" t="inlineStr">
+      <c r="A203" s="6" t="inlineStr">
         <is>
           <t>GS Green Bond Short Duration I Hedged i Cap GBP</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B203" s="6" t="inlineStr">
         <is>
           <t>LU1922483612</t>
         </is>
@@ -3854,12 +3854,12 @@
       </c>
     </row>
     <row r="204" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A204" t="inlineStr">
+      <c r="A204" s="6" t="inlineStr">
         <is>
           <t>GS India Equity Portfolio I</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B204" s="6" t="inlineStr">
         <is>
           <t>LU0333810934</t>
         </is>
@@ -3871,12 +3871,12 @@
       </c>
     </row>
     <row r="205" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="6" t="inlineStr">
         <is>
           <t>GS India Equity Portfolio I Acc</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B205" s="6" t="inlineStr">
         <is>
           <t>LU0333811072</t>
         </is>
@@ -3888,12 +3888,12 @@
       </c>
     </row>
     <row r="206" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A206" t="inlineStr">
+      <c r="A206" s="6" t="inlineStr">
         <is>
           <t>GS India Equity Portfolio I GBP</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B206" s="6" t="inlineStr">
         <is>
           <t>LU1268608111</t>
         </is>
@@ -3905,12 +3905,12 @@
       </c>
     </row>
     <row r="207" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A207" t="inlineStr">
+      <c r="A207" s="6" t="inlineStr">
         <is>
           <t>GS Japan Equity Partners Portfolio I (Snap) Acc GBP</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B207" s="6" t="inlineStr">
         <is>
           <t>LU1220104142</t>
         </is>
@@ -3922,12 +3922,12 @@
       </c>
     </row>
     <row r="208" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A208" t="inlineStr">
+      <c r="A208" s="6" t="inlineStr">
         <is>
           <t>GS Japan Equity Partners Portfolio I Hedged (Snap) Acc GBP</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B208" s="6" t="inlineStr">
         <is>
           <t>LU1220104654</t>
         </is>
@@ -3939,12 +3939,12 @@
       </c>
     </row>
     <row r="209" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A209" t="inlineStr">
+      <c r="A209" s="6" t="inlineStr">
         <is>
           <t>GS Japan Equity Partners Portfolio R (Snap) Cap GBP</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B209" s="6" t="inlineStr">
         <is>
           <t>LU2642427624</t>
         </is>
@@ -3956,12 +3956,12 @@
       </c>
     </row>
     <row r="210" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A210" t="inlineStr">
+      <c r="A210" s="6" t="inlineStr">
         <is>
           <t>GS Japan Equity Partners Portfolio R (Snap) Inc GBP</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B210" s="6" t="inlineStr">
         <is>
           <t>LU2254254183</t>
         </is>
@@ -3973,12 +3973,12 @@
       </c>
     </row>
     <row r="211" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A211" t="inlineStr">
+      <c r="A211" s="6" t="inlineStr">
         <is>
           <t>GS Japan Equity Partners Portfolio R Hedged (Snap) Acc GBP</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B211" s="6" t="inlineStr">
         <is>
           <t>LU1217871489</t>
         </is>
@@ -3990,12 +3990,12 @@
       </c>
     </row>
     <row r="212" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A212" t="inlineStr">
+      <c r="A212" s="6" t="inlineStr">
         <is>
           <t>GS Japan Equity Portfolio I Hedged (Snap) GBP</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>LU1474194062</t>
         </is>
@@ -4007,12 +4007,12 @@
       </c>
     </row>
     <row r="213" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A213" t="inlineStr">
+      <c r="A213" s="6" t="inlineStr">
         <is>
           <t>GS Japan Equity Portfolio R Hedged (Snap) GBP</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B213" s="6" t="inlineStr">
         <is>
           <t>LU1474193411</t>
         </is>
@@ -4024,12 +4024,12 @@
       </c>
     </row>
     <row r="214" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A214" t="inlineStr">
+      <c r="A214" s="6" t="inlineStr">
         <is>
           <t>GS Japan Equity Portfolio R Snap GBP</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B214" s="6" t="inlineStr">
         <is>
           <t>LU0858289597</t>
         </is>
@@ -4041,12 +4041,12 @@
       </c>
     </row>
     <row r="215" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A215" t="inlineStr">
+      <c r="A215" s="6" t="inlineStr">
         <is>
           <t>GS Quartix Modified Strategy on the Bloomberg Commodity Index Total Return Pfl C Unhedged Acc GBP</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B215" s="6" t="inlineStr">
         <is>
           <t>LU0729061019</t>
         </is>
@@ -4058,12 +4058,12 @@
       </c>
     </row>
     <row r="216" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A216" t="inlineStr">
+      <c r="A216" s="6" t="inlineStr">
         <is>
           <t>GS Quartix Modified Strategy on the Bloomberg Commodity Index Total Return Pfl R Unhedged Acc GBP</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B216" s="6" t="inlineStr">
         <is>
           <t>LU0875392457</t>
         </is>
@@ -4075,12 +4075,12 @@
       </c>
     </row>
     <row r="217" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A217" t="inlineStr">
+      <c r="A217" s="6" t="inlineStr">
         <is>
           <t>GS Short Duration Opportunistic Corporate Bond Portfolio R Acc</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B217" s="6" t="inlineStr">
         <is>
           <t>LU0830676598</t>
         </is>
@@ -4092,12 +4092,12 @@
       </c>
     </row>
     <row r="218" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="6" t="inlineStr">
         <is>
           <t>GS Short Duration Opportunistic Corporate Bond Portfolio R Hedged GBP</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B218" s="6" t="inlineStr">
         <is>
           <t>LU0858301129</t>
         </is>
@@ -4109,12 +4109,12 @@
       </c>
     </row>
     <row r="219" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A219" t="inlineStr">
+      <c r="A219" s="6" t="inlineStr">
         <is>
           <t>GS Sovereign Green Bond I Cap GBP</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B219" s="6" t="inlineStr">
         <is>
           <t>LU2400966417</t>
         </is>
@@ -4126,12 +4126,12 @@
       </c>
     </row>
     <row r="220" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A220" t="inlineStr">
+      <c r="A220" s="6" t="inlineStr">
         <is>
           <t>GS Sovereign Green Bond R Dis</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B220" s="6" t="inlineStr">
         <is>
           <t>LU2349459128</t>
         </is>
@@ -4143,12 +4143,12 @@
       </c>
     </row>
     <row r="221" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A221" t="inlineStr">
+      <c r="A221" s="6" t="inlineStr">
         <is>
           <t>GS Sterling Liquid Reserves Institutional Acc</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B221" s="6" t="inlineStr">
         <is>
           <t>IE0031296233</t>
         </is>
@@ -4160,12 +4160,12 @@
       </c>
     </row>
     <row r="222" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A222" t="inlineStr">
+      <c r="A222" s="6" t="inlineStr">
         <is>
           <t>GS Sterling Liquid Reserves R Acc</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B222" s="6" t="inlineStr">
         <is>
           <t>IE00B8KJ1435</t>
         </is>
@@ -4177,12 +4177,12 @@
       </c>
     </row>
     <row r="223" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A223" t="inlineStr">
+      <c r="A223" s="6" t="inlineStr">
         <is>
           <t>GS US Equity ESG Portfolio I GBP</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B223" s="6" t="inlineStr">
         <is>
           <t>LU0543872708</t>
         </is>
@@ -4194,12 +4194,12 @@
       </c>
     </row>
     <row r="224" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A224" t="inlineStr">
+      <c r="A224" s="6" t="inlineStr">
         <is>
           <t>GSI Global Aware Focused Value B Acc GBP</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B224" s="6" t="inlineStr">
         <is>
           <t>IE000AYHQP03</t>
         </is>
@@ -4211,12 +4211,12 @@
       </c>
     </row>
     <row r="225" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A225" t="inlineStr">
+      <c r="A225" s="6" t="inlineStr">
         <is>
           <t>GSI Global Aware Value A Dis GBP</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B225" s="6" t="inlineStr">
         <is>
           <t>IE00BZ036B68</t>
         </is>
@@ -4228,12 +4228,12 @@
       </c>
     </row>
     <row r="226" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A226" t="inlineStr">
+      <c r="A226" s="6" t="inlineStr">
         <is>
           <t>GuardCap Global Equity I GBP</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B226" s="6" t="inlineStr">
         <is>
           <t>IE00BVSS1C10</t>
         </is>
@@ -4245,12 +4245,12 @@
       </c>
     </row>
     <row r="227" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A227" t="inlineStr">
+      <c r="A227" s="6" t="inlineStr">
         <is>
           <t>GuardCap Global Equity I Inc GBP</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B227" s="6" t="inlineStr">
         <is>
           <t>IE00BF2T2J22</t>
         </is>
@@ -4262,12 +4262,12 @@
       </c>
     </row>
     <row r="228" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A228" t="inlineStr">
+      <c r="A228" s="6" t="inlineStr">
         <is>
           <t>Guinness Asian Equity Income Y Acc GBP</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B228" s="6" t="inlineStr">
         <is>
           <t>IE00BDHSRD90</t>
         </is>
@@ -4279,12 +4279,12 @@
       </c>
     </row>
     <row r="229" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A229" t="inlineStr">
+      <c r="A229" s="6" t="inlineStr">
         <is>
           <t>Guinness Asian Equity Income Y Dis GBP</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B229" s="6" t="inlineStr">
         <is>
           <t>IE00BDHSRF15</t>
         </is>
@@ -4296,12 +4296,12 @@
       </c>
     </row>
     <row r="230" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A230" t="inlineStr">
+      <c r="A230" s="6" t="inlineStr">
         <is>
           <t>Guinness Best of Asia F Acc GBP</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B230" s="6" t="inlineStr">
         <is>
           <t>IE00BF2VG183</t>
         </is>
@@ -4313,12 +4313,12 @@
       </c>
     </row>
     <row r="231" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A231" t="inlineStr">
+      <c r="A231" s="6" t="inlineStr">
         <is>
           <t>Guinness Emerging Markets Equity Income F Dist GBP</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B231" s="6" t="inlineStr">
         <is>
           <t>IE00BYV24X31</t>
         </is>
@@ -4330,12 +4330,12 @@
       </c>
     </row>
     <row r="232" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A232" t="inlineStr">
+      <c r="A232" s="6" t="inlineStr">
         <is>
           <t>Guinness Emerging Markets Equity Income Y Acc GBP</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B232" s="6" t="inlineStr">
         <is>
           <t>IE00BYV24Q63</t>
         </is>
@@ -4347,12 +4347,12 @@
       </c>
     </row>
     <row r="233" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A233" t="inlineStr">
+      <c r="A233" s="6" t="inlineStr">
         <is>
           <t>Guinness Emerging Markets Equity Income Y Inc GBP</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B233" s="6" t="inlineStr">
         <is>
           <t>IE00BYV24R70</t>
         </is>
@@ -4364,12 +4364,12 @@
       </c>
     </row>
     <row r="234" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A234" t="inlineStr">
+      <c r="A234" s="6" t="inlineStr">
         <is>
           <t>Guinness European Equity Income F Acc GBP</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B234" s="6" t="inlineStr">
         <is>
           <t>IE000YNWUZY0</t>
         </is>
@@ -4381,12 +4381,12 @@
       </c>
     </row>
     <row r="235" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A235" t="inlineStr">
+      <c r="A235" s="6" t="inlineStr">
         <is>
           <t>Guinness European Equity Income F Dis GBP</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B235" s="6" t="inlineStr">
         <is>
           <t>IE00BGHQF300</t>
         </is>
@@ -4398,12 +4398,12 @@
       </c>
     </row>
     <row r="236" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A236" t="inlineStr">
+      <c r="A236" s="6" t="inlineStr">
         <is>
           <t>Guinness European Equity Income Y Acc GBP</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B236" s="6" t="inlineStr">
         <is>
           <t>IE00BYVHVZ98</t>
         </is>
@@ -4415,12 +4415,12 @@
       </c>
     </row>
     <row r="237" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A237" t="inlineStr">
+      <c r="A237" s="6" t="inlineStr">
         <is>
           <t>Guinness European Equity Income Y Dis GBP</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B237" s="6" t="inlineStr">
         <is>
           <t>IE00BYVHWJ06</t>
         </is>
@@ -4432,12 +4432,12 @@
       </c>
     </row>
     <row r="238" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A238" t="inlineStr">
+      <c r="A238" s="6" t="inlineStr">
         <is>
           <t>Guinness Global Energy Y Acc GBP</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B238" s="6" t="inlineStr">
         <is>
           <t>IE00B6XV0016</t>
         </is>
@@ -4449,12 +4449,12 @@
       </c>
     </row>
     <row r="239" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A239" t="inlineStr">
+      <c r="A239" s="6" t="inlineStr">
         <is>
           <t>Guinness Global Equity Income Y Acc GBP</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B239" s="6" t="inlineStr">
         <is>
           <t>IE00BVYPNY24</t>
         </is>
@@ -4466,12 +4466,12 @@
       </c>
     </row>
     <row r="240" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A240" t="inlineStr">
+      <c r="A240" s="6" t="inlineStr">
         <is>
           <t>Guinness Global Equity Income Y Dis GBP</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B240" s="6" t="inlineStr">
         <is>
           <t>IE00BVYPP131</t>
         </is>
@@ -4483,12 +4483,12 @@
       </c>
     </row>
     <row r="241" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A241" t="inlineStr">
+      <c r="A241" s="6" t="inlineStr">
         <is>
           <t>Guinness Global Equity Income Z Acc GBP</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B241" s="6" t="inlineStr">
         <is>
           <t>IE000P7D8CD0</t>
         </is>
@@ -4500,12 +4500,12 @@
       </c>
     </row>
     <row r="242" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A242" t="inlineStr">
+      <c r="A242" s="6" t="inlineStr">
         <is>
           <t>Guinness Global Innovators Y Acc GBP</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B242" s="6" t="inlineStr">
         <is>
           <t>IE00BQXX3K83</t>
         </is>
@@ -4517,12 +4517,12 @@
       </c>
     </row>
     <row r="243" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A243" t="inlineStr">
+      <c r="A243" s="6" t="inlineStr">
         <is>
           <t>Guinness Global Money Managers Y Acc GBP</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B243" s="6" t="inlineStr">
         <is>
           <t>IE00B7MJHM43</t>
         </is>
@@ -4534,12 +4534,12 @@
       </c>
     </row>
     <row r="244" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A244" t="inlineStr">
+      <c r="A244" s="6" t="inlineStr">
         <is>
           <t>Guinness Global Quality Mid Cap F GBP Acc</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B244" s="6" t="inlineStr">
         <is>
           <t>IE00BN0W3305</t>
         </is>
@@ -4551,12 +4551,12 @@
       </c>
     </row>
     <row r="245" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A245" t="inlineStr">
+      <c r="A245" s="6" t="inlineStr">
         <is>
           <t>Guinness Global Quality Mid Cap Y GBP Acc</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B245" s="6" t="inlineStr">
         <is>
           <t>IE00BN0W3073</t>
         </is>
@@ -4568,12 +4568,12 @@
       </c>
     </row>
     <row r="246" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A246" t="inlineStr">
+      <c r="A246" s="6" t="inlineStr">
         <is>
           <t>Guinness Global Real Assets Y Acc GBP</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B246" s="6" t="inlineStr">
         <is>
           <t>IE00012CHFP3</t>
         </is>
@@ -4585,12 +4585,12 @@
       </c>
     </row>
     <row r="247" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A247" t="inlineStr">
+      <c r="A247" s="6" t="inlineStr">
         <is>
           <t>Guinness Greater China F Acc GBP</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B247" s="6" t="inlineStr">
         <is>
           <t>IE00BZ08YY02</t>
         </is>
@@ -4602,12 +4602,12 @@
       </c>
     </row>
     <row r="248" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A248" t="inlineStr">
+      <c r="A248" s="6" t="inlineStr">
         <is>
           <t>Guinness Greater China Y Acc GBP</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B248" s="6" t="inlineStr">
         <is>
           <t>IE00BZ08YV70</t>
         </is>
@@ -4619,12 +4619,12 @@
       </c>
     </row>
     <row r="249" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A249" t="inlineStr">
+      <c r="A249" s="6" t="inlineStr">
         <is>
           <t>Guinness Multi-Asset Balanced Y Acc GBP</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B249" s="6" t="inlineStr">
         <is>
           <t>IE00BG5QRB49</t>
         </is>
@@ -4636,12 +4636,12 @@
       </c>
     </row>
     <row r="250" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A250" t="inlineStr">
+      <c r="A250" s="6" t="inlineStr">
         <is>
           <t>Guinness Multi-Asset Growth Y Acc GBP</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B250" s="6" t="inlineStr">
         <is>
           <t>IE00BG5QRW51</t>
         </is>
@@ -4653,12 +4653,12 @@
       </c>
     </row>
     <row r="251" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A251" t="inlineStr">
+      <c r="A251" s="6" t="inlineStr">
         <is>
           <t>Guinness Sustainable Energy Y Acc GBP</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B251" s="6" t="inlineStr">
         <is>
           <t>IE00BFYV9L73</t>
         </is>
@@ -4670,12 +4670,12 @@
       </c>
     </row>
     <row r="252" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A252" t="inlineStr">
+      <c r="A252" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Global Short Duration Income Opportunities U Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B252" s="6" t="inlineStr">
         <is>
           <t>IE00BLWF5R19</t>
         </is>
@@ -4687,12 +4687,12 @@
       </c>
     </row>
     <row r="253" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A253" t="inlineStr">
+      <c r="A253" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Global Smaller Companies Fund I Acc GBP</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B253" s="6" t="inlineStr">
         <is>
           <t>GB00BP47T486</t>
         </is>
@@ -4704,12 +4704,12 @@
       </c>
     </row>
     <row r="254" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A254" t="inlineStr">
+      <c r="A254" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Global Sustainable Equity I Acc</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B254" s="6" t="inlineStr">
         <is>
           <t>GB00B71DPP64</t>
         </is>
@@ -4721,12 +4721,12 @@
       </c>
     </row>
     <row r="255" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A255" t="inlineStr">
+      <c r="A255" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Global Sustainable Equity I Inc</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B255" s="6" t="inlineStr">
         <is>
           <t>GB0005030043</t>
         </is>
@@ -4738,12 +4738,12 @@
       </c>
     </row>
     <row r="256" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A256" t="inlineStr">
+      <c r="A256" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Global Technology Leaders H2 Acc GBP</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B256" s="6" t="inlineStr">
         <is>
           <t>LU1276832638</t>
         </is>
@@ -4755,12 +4755,12 @@
       </c>
     </row>
     <row r="257" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A257" t="inlineStr">
+      <c r="A257" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Global Technology Leaders I Acc</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B257" s="6" t="inlineStr">
         <is>
           <t>GB0007716078</t>
         </is>
@@ -4772,12 +4772,12 @@
       </c>
     </row>
     <row r="258" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A258" t="inlineStr">
+      <c r="A258" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Horizon Asian Dividend Income I3q Inc GBP</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B258" s="6" t="inlineStr">
         <is>
           <t>LU0277002928</t>
         </is>
@@ -4789,12 +4789,12 @@
       </c>
     </row>
     <row r="259" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A259" t="inlineStr">
+      <c r="A259" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Horizon Biotechnology IU2 Acc GBP</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B259" s="6" t="inlineStr">
         <is>
           <t>LU2832952142</t>
         </is>
@@ -4806,12 +4806,12 @@
       </c>
     </row>
     <row r="260" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A260" t="inlineStr">
+      <c r="A260" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Horizon Euro Corporate Bond H3 H Inc GBP</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B260" s="6" t="inlineStr">
         <is>
           <t>LU1276833289</t>
         </is>
@@ -4823,12 +4823,12 @@
       </c>
     </row>
     <row r="261" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A261" t="inlineStr">
+      <c r="A261" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Horizon Global Property Equities H2 Acc GBP</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B261" s="6" t="inlineStr">
         <is>
           <t>LU1276832984</t>
         </is>
@@ -4840,12 +4840,12 @@
       </c>
     </row>
     <row r="262" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A262" t="inlineStr">
+      <c r="A262" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Horizon Global Property Equities H2 Acc USD</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B262" s="6" t="inlineStr">
         <is>
           <t>LU0892274530</t>
         </is>
@@ -4857,12 +4857,12 @@
       </c>
     </row>
     <row r="263" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A263" t="inlineStr">
+      <c r="A263" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Horizon Global Property Equities H2 H Acc EUR</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B263" s="6" t="inlineStr">
         <is>
           <t>LU0976557073</t>
         </is>
@@ -4874,12 +4874,12 @@
       </c>
     </row>
     <row r="264" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A264" t="inlineStr">
+      <c r="A264" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Horizon Japanese Smaller Companies H2 Acc USD</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B264" s="6" t="inlineStr">
         <is>
           <t>LU0976557230</t>
         </is>
@@ -4891,12 +4891,12 @@
       </c>
     </row>
     <row r="265" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A265" t="inlineStr">
+      <c r="A265" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Horizon Pan European Property Equities H2 H Acc EUR</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B265" s="6" t="inlineStr">
         <is>
           <t>LU0892274969</t>
         </is>
@@ -4908,12 +4908,12 @@
       </c>
     </row>
     <row r="266" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A266" t="inlineStr">
+      <c r="A266" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Horizon Pan European Property Equities I2 Acc EUR</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B266" s="6" t="inlineStr">
         <is>
           <t>LU0196034317</t>
         </is>
@@ -4925,12 +4925,12 @@
       </c>
     </row>
     <row r="267" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A267" t="inlineStr">
+      <c r="A267" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Horizon Strategic Bond GU2 H GBP</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B267" s="6" t="inlineStr">
         <is>
           <t>LU1627466771</t>
         </is>
@@ -4942,12 +4942,12 @@
       </c>
     </row>
     <row r="268" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A268" t="inlineStr">
+      <c r="A268" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Horizon Strategic Bond GU3q H GBP</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B268" s="6" t="inlineStr">
         <is>
           <t>LU1627466425</t>
         </is>
@@ -4959,12 +4959,12 @@
       </c>
     </row>
     <row r="269" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A269" t="inlineStr">
+      <c r="A269" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Inst High Alpha UK Equity I Inc</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B269" s="6" t="inlineStr">
         <is>
           <t>GB00B1WPDJ97</t>
         </is>
@@ -4976,12 +4976,12 @@
       </c>
     </row>
     <row r="270" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A270" t="inlineStr">
+      <c r="A270" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Inst Japan Index Opportunities I Acc</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>GB00B0LZBB16</t>
         </is>
@@ -4993,12 +4993,12 @@
       </c>
     </row>
     <row r="271" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A271" t="inlineStr">
+      <c r="A271" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Inst North American Index Opportunities I Acc</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B271" s="6" t="inlineStr">
         <is>
           <t>GB00B00K2Z88</t>
         </is>
@@ -5010,12 +5010,12 @@
       </c>
     </row>
     <row r="272" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A272" t="inlineStr">
+      <c r="A272" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Inst Overseas Bond I Acc</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B272" s="6" t="inlineStr">
         <is>
           <t>GB0007674467</t>
         </is>
@@ -5027,12 +5027,12 @@
       </c>
     </row>
     <row r="273" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A273" t="inlineStr">
+      <c r="A273" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Inst Overseas Bond I Inc</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B273" s="6" t="inlineStr">
         <is>
           <t>GB0007674244</t>
         </is>
@@ -5044,12 +5044,12 @@
       </c>
     </row>
     <row r="274" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A274" t="inlineStr">
+      <c r="A274" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Inst UK Index Opportunities Trust A Acc</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B274" s="6" t="inlineStr">
         <is>
           <t>GB00BKTDJZ77</t>
         </is>
@@ -5061,12 +5061,12 @@
       </c>
     </row>
     <row r="275" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A275" t="inlineStr">
+      <c r="A275" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Inst UK Index Opportunities Trust A Inc</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B275" s="6" t="inlineStr">
         <is>
           <t>GB00BKTDK099</t>
         </is>
@@ -5078,12 +5078,12 @@
       </c>
     </row>
     <row r="276" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A276" t="inlineStr">
+      <c r="A276" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Inst UK Index Opportunities Trust I Acc</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B276" s="6" t="inlineStr">
         <is>
           <t>GB00B02ZBX27</t>
         </is>
@@ -5095,12 +5095,12 @@
       </c>
     </row>
     <row r="277" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A277" t="inlineStr">
+      <c r="A277" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Japan Opportunities I Acc</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B277" s="6" t="inlineStr">
         <is>
           <t>GB0007685026</t>
         </is>
@@ -5112,12 +5112,12 @@
       </c>
     </row>
     <row r="278" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A278" t="inlineStr">
+      <c r="A278" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Multi Asset Credit I Hedged Acc Gross GBP</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B278" s="6" t="inlineStr">
         <is>
           <t>GB00B7VD8806</t>
         </is>
@@ -5129,12 +5129,12 @@
       </c>
     </row>
     <row r="279" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A279" t="inlineStr">
+      <c r="A279" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Multi-Asset Absolute Return I Acc</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B279" s="6" t="inlineStr">
         <is>
           <t>GB00B8113P38</t>
         </is>
@@ -5146,12 +5146,12 @@
       </c>
     </row>
     <row r="280" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A280" t="inlineStr">
+      <c r="A280" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Multi-Manager Active I Acc</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
+      <c r="B280" s="6" t="inlineStr">
         <is>
           <t>GB00B83VFR76</t>
         </is>
@@ -5163,12 +5163,12 @@
       </c>
     </row>
     <row r="281" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A281" t="inlineStr">
+      <c r="A281" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Multi-Manager Distribution I Inc</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B281" s="6" t="inlineStr">
         <is>
           <t>GB00B87K9900</t>
         </is>
@@ -5180,12 +5180,12 @@
       </c>
     </row>
     <row r="282" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A282" t="inlineStr">
+      <c r="A282" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Multi-Manager Diversified B Acc</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
+      <c r="B282" s="6" t="inlineStr">
         <is>
           <t>GB00B1L74484</t>
         </is>
@@ -5197,12 +5197,12 @@
       </c>
     </row>
     <row r="283" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A283" t="inlineStr">
+      <c r="A283" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Multi-Manager Diversified I Inc</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
+      <c r="B283" s="6" t="inlineStr">
         <is>
           <t>GB00B5TPWM66</t>
         </is>
@@ -5214,12 +5214,12 @@
       </c>
     </row>
     <row r="284" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A284" t="inlineStr">
+      <c r="A284" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Multi-Manager Global Select E Acc</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
+      <c r="B284" s="6" t="inlineStr">
         <is>
           <t>GB00BJ0LG858</t>
         </is>
@@ -5231,12 +5231,12 @@
       </c>
     </row>
     <row r="285" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A285" t="inlineStr">
+      <c r="A285" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Multi-Manager Global Select I Acc</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
+      <c r="B285" s="6" t="inlineStr">
         <is>
           <t>GB00B8B6NJ28</t>
         </is>
@@ -5248,12 +5248,12 @@
       </c>
     </row>
     <row r="286" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A286" t="inlineStr">
+      <c r="A286" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Multi-Manager Income &amp; Growth I Acc</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
+      <c r="B286" s="6" t="inlineStr">
         <is>
           <t>GB00BFDTFW55</t>
         </is>
@@ -5265,12 +5265,12 @@
       </c>
     </row>
     <row r="287" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A287" t="inlineStr">
+      <c r="A287" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Multi-Manager Income &amp; Growth I Inc</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
+      <c r="B287" s="6" t="inlineStr">
         <is>
           <t>GB00B88HSJ33</t>
         </is>
@@ -5282,12 +5282,12 @@
       </c>
     </row>
     <row r="288" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A288" t="inlineStr">
+      <c r="A288" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Multi-Manager Managed I Acc</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
+      <c r="B288" s="6" t="inlineStr">
         <is>
           <t>GB00B7JZZK97</t>
         </is>
@@ -5299,12 +5299,12 @@
       </c>
     </row>
     <row r="289" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A289" t="inlineStr">
+      <c r="A289" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Sterling Bond Unit Trust I Acc</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
+      <c r="B289" s="6" t="inlineStr">
         <is>
           <t>GB00B8GJGW07</t>
         </is>
@@ -5316,12 +5316,12 @@
       </c>
     </row>
     <row r="290" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A290" t="inlineStr">
+      <c r="A290" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Sterling Bond Unit Trust I Inc</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
+      <c r="B290" s="6" t="inlineStr">
         <is>
           <t>GB00B6XY7V09</t>
         </is>
@@ -5333,12 +5333,12 @@
       </c>
     </row>
     <row r="291" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A291" t="inlineStr">
+      <c r="A291" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Strategic Bond F Acc</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
+      <c r="B291" s="6" t="inlineStr">
         <is>
           <t>GB00BMDBB886</t>
         </is>
@@ -5350,12 +5350,12 @@
       </c>
     </row>
     <row r="292" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A292" t="inlineStr">
+      <c r="A292" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Sustainable Future Technologies G Acc GBP</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
+      <c r="B292" s="6" t="inlineStr">
         <is>
           <t>GB00BN7CMY70</t>
         </is>
@@ -5367,12 +5367,12 @@
       </c>
     </row>
     <row r="293" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A293" t="inlineStr">
+      <c r="A293" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson Sustainable Future Technologies I Acc GBP</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
+      <c r="B293" s="6" t="inlineStr">
         <is>
           <t>GB00BN7CMW56</t>
         </is>
@@ -5384,12 +5384,12 @@
       </c>
     </row>
     <row r="294" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A294" t="inlineStr">
+      <c r="A294" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson UK Alpha E Acc</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
+      <c r="B294" s="6" t="inlineStr">
         <is>
           <t>GB00BJ0LGL85</t>
         </is>
@@ -5401,12 +5401,12 @@
       </c>
     </row>
     <row r="295" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A295" t="inlineStr">
+      <c r="A295" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson UK Alpha I Acc</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
+      <c r="B295" s="6" t="inlineStr">
         <is>
           <t>GB0030956832</t>
         </is>
@@ -5418,12 +5418,12 @@
       </c>
     </row>
     <row r="296" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A296" t="inlineStr">
+      <c r="A296" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson UK Equity Income &amp; Growth I Acc</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
+      <c r="B296" s="6" t="inlineStr">
         <is>
           <t>GB0007494221</t>
         </is>
@@ -5435,12 +5435,12 @@
       </c>
     </row>
     <row r="297" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A297" t="inlineStr">
+      <c r="A297" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson UK Equity Income &amp; Growth I Inc</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
+      <c r="B297" s="6" t="inlineStr">
         <is>
           <t>GB0007493470</t>
         </is>
@@ -5452,12 +5452,12 @@
       </c>
     </row>
     <row r="298" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A298" t="inlineStr">
+      <c r="A298" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson UK Responsible Income G Acc</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
+      <c r="B298" s="6" t="inlineStr">
         <is>
           <t>GB00BMX58Y51</t>
         </is>
@@ -5469,12 +5469,12 @@
       </c>
     </row>
     <row r="299" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A299" t="inlineStr">
+      <c r="A299" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson UK Responsible Income G Inc</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
+      <c r="B299" s="6" t="inlineStr">
         <is>
           <t>GB00BMX58Z68</t>
         </is>
@@ -5486,12 +5486,12 @@
       </c>
     </row>
     <row r="300" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A300" t="inlineStr">
+      <c r="A300" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson UK Smaller Companies E Acc</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B300" s="6" t="inlineStr">
         <is>
           <t>GB00BJ0LGV83</t>
         </is>
@@ -5503,12 +5503,12 @@
       </c>
     </row>
     <row r="301" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A301" t="inlineStr">
+      <c r="A301" s="6" t="inlineStr">
         <is>
           <t>Janus Henderson UK Smaller Companies I Acc</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B301" s="6" t="inlineStr">
         <is>
           <t>GB0007447625</t>
         </is>
@@ -5520,12 +5520,12 @@
       </c>
     </row>
     <row r="302" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A302" t="inlineStr">
+      <c r="A302" s="6" t="inlineStr">
         <is>
           <t>Liontrust GF Global Dividend C10 Inc GBP</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
+      <c r="B302" s="6" t="inlineStr">
         <is>
           <t>IE000M9DFQN6</t>
         </is>
@@ -5537,12 +5537,12 @@
       </c>
     </row>
     <row r="303" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A303" t="inlineStr">
+      <c r="A303" s="6" t="inlineStr">
         <is>
           <t>Liontrust GF Global Innovation Fund C10 Acc GBP</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
+      <c r="B303" s="6" t="inlineStr">
         <is>
           <t>IE000O7JFSR2</t>
         </is>
@@ -5554,12 +5554,12 @@
       </c>
     </row>
     <row r="304" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A304" t="inlineStr">
+      <c r="A304" s="6" t="inlineStr">
         <is>
           <t>Liontrust GF Global Short Dated Corporate Bond C5 Acc GBP</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
+      <c r="B304" s="6" t="inlineStr">
         <is>
           <t>IE00BD85PY62</t>
         </is>
@@ -5571,12 +5571,12 @@
       </c>
     </row>
     <row r="305" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A305" t="inlineStr">
+      <c r="A305" s="6" t="inlineStr">
         <is>
           <t>Liontrust GF High Yield Bond C Dis GBP</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B305" s="6" t="inlineStr">
         <is>
           <t>IE00BFXZFS96</t>
         </is>
@@ -5588,12 +5588,12 @@
       </c>
     </row>
     <row r="306" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A306" t="inlineStr">
+      <c r="A306" s="6" t="inlineStr">
         <is>
           <t>Liontrust GF High Yield Bond C5 Acc GBP</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
+      <c r="B306" s="6" t="inlineStr">
         <is>
           <t>IE00BFXZFR89</t>
         </is>
@@ -5605,12 +5605,12 @@
       </c>
     </row>
     <row r="307" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A307" t="inlineStr">
+      <c r="A307" s="6" t="inlineStr">
         <is>
           <t>Liontrust GF Sustainable Future US Growth B5 Acc USD</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
+      <c r="B307" s="6" t="inlineStr">
         <is>
           <t>IE0007RMU077</t>
         </is>
@@ -5622,12 +5622,12 @@
       </c>
     </row>
     <row r="308" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A308" t="inlineStr">
+      <c r="A308" s="6" t="inlineStr">
         <is>
           <t>Liontrust GF Sustainable Future US Growth C5 Acc GBP</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
+      <c r="B308" s="6" t="inlineStr">
         <is>
           <t>IE000RQI4QR2</t>
         </is>
@@ -5639,12 +5639,12 @@
       </c>
     </row>
     <row r="309" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A309" t="inlineStr">
+      <c r="A309" s="6" t="inlineStr">
         <is>
           <t>Liontrust Global Alpha B GBP</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
+      <c r="B309" s="6" t="inlineStr">
         <is>
           <t>GB00BMWB3R26</t>
         </is>
@@ -5656,12 +5656,12 @@
       </c>
     </row>
     <row r="310" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A310" t="inlineStr">
+      <c r="A310" s="6" t="inlineStr">
         <is>
           <t>Liontrust Global Alpha C Acc</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
+      <c r="B310" s="6" t="inlineStr">
         <is>
           <t>GB0031190555</t>
         </is>
@@ -5673,12 +5673,12 @@
       </c>
     </row>
     <row r="311" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A311" t="inlineStr">
+      <c r="A311" s="6" t="inlineStr">
         <is>
           <t>Liontrust Global Dividend M Acc GBP</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
+      <c r="B311" s="6" t="inlineStr">
         <is>
           <t>GB00BL839J93</t>
         </is>
@@ -5690,12 +5690,12 @@
       </c>
     </row>
     <row r="312" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A312" t="inlineStr">
+      <c r="A312" s="6" t="inlineStr">
         <is>
           <t>Liontrust Global Dividend M Inc GBP</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
+      <c r="B312" s="6" t="inlineStr">
         <is>
           <t>GB00BL839H79</t>
         </is>
@@ -5707,12 +5707,12 @@
       </c>
     </row>
     <row r="313" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A313" t="inlineStr">
+      <c r="A313" s="6" t="inlineStr">
         <is>
           <t>Liontrust Global Innovation C Acc GBP</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
+      <c r="B313" s="6" t="inlineStr">
         <is>
           <t>GB00B8DLY478</t>
         </is>
@@ -5724,12 +5724,12 @@
       </c>
     </row>
     <row r="314" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A314" t="inlineStr">
+      <c r="A314" s="6" t="inlineStr">
         <is>
           <t>Liontrust Global Smaller Companies C Acc GBP</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
+      <c r="B314" s="6" t="inlineStr">
         <is>
           <t>GB00B29MXF68</t>
         </is>
@@ -5741,12 +5741,12 @@
       </c>
     </row>
     <row r="315" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A315" t="inlineStr">
+      <c r="A315" s="6" t="inlineStr">
         <is>
           <t>Liontrust Global Technology C Acc GBP</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
+      <c r="B315" s="6" t="inlineStr">
         <is>
           <t>GB00BYXZ5N79</t>
         </is>
@@ -5758,12 +5758,12 @@
       </c>
     </row>
     <row r="316" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A316" t="inlineStr">
+      <c r="A316" s="6" t="inlineStr">
         <is>
           <t>Liontrust Income C Acc</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
+      <c r="B316" s="6" t="inlineStr">
         <is>
           <t>GB00B8JCR452</t>
         </is>
@@ -5775,12 +5775,12 @@
       </c>
     </row>
     <row r="317" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A317" t="inlineStr">
+      <c r="A317" s="6" t="inlineStr">
         <is>
           <t>Liontrust Income C Inc</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
+      <c r="B317" s="6" t="inlineStr">
         <is>
           <t>GB00B8L7B355</t>
         </is>
@@ -5792,12 +5792,12 @@
       </c>
     </row>
     <row r="318" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A318" t="inlineStr">
+      <c r="A318" s="6" t="inlineStr">
         <is>
           <t>Liontrust India C Acc GBP</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B318" s="6" t="inlineStr">
         <is>
           <t>GB00B1L6DV51</t>
         </is>
@@ -5809,12 +5809,12 @@
       </c>
     </row>
     <row r="319" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A319" t="inlineStr">
+      <c r="A319" s="6" t="inlineStr">
         <is>
           <t>Liontrust Japan Equity C Acc GBP</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B319" s="6" t="inlineStr">
         <is>
           <t>GB00BXDZFF23</t>
         </is>
@@ -5826,12 +5826,12 @@
       </c>
     </row>
     <row r="320" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A320" t="inlineStr">
+      <c r="A320" s="6" t="inlineStr">
         <is>
           <t>Liontrust Japan Equity C Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
+      <c r="B320" s="6" t="inlineStr">
         <is>
           <t>GB00BXDZFG30</t>
         </is>
@@ -5843,12 +5843,12 @@
       </c>
     </row>
     <row r="321" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A321" t="inlineStr">
+      <c r="A321" s="6" t="inlineStr">
         <is>
           <t>Liontrust Latin America C Acc GBP</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
+      <c r="B321" s="6" t="inlineStr">
         <is>
           <t>GB00B909HH53</t>
         </is>
@@ -5860,12 +5860,12 @@
       </c>
     </row>
     <row r="322" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A322" t="inlineStr">
+      <c r="A322" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Blended Growth A Acc</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
+      <c r="B322" s="6" t="inlineStr">
         <is>
           <t>GB00B820T519</t>
         </is>
@@ -5877,12 +5877,12 @@
       </c>
     </row>
     <row r="323" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A323" t="inlineStr">
+      <c r="A323" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Blended Growth S Acc</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
+      <c r="B323" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW5H67</t>
         </is>
@@ -5894,12 +5894,12 @@
       </c>
     </row>
     <row r="324" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A324" t="inlineStr">
+      <c r="A324" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Blended Intermediate S Acc</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
+      <c r="B324" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW5K96</t>
         </is>
@@ -5911,12 +5911,12 @@
       </c>
     </row>
     <row r="325" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A325" t="inlineStr">
+      <c r="A325" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Blended Intermediate S Inc</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
+      <c r="B325" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW5L04</t>
         </is>
@@ -5928,12 +5928,12 @@
       </c>
     </row>
     <row r="326" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A326" t="inlineStr">
+      <c r="A326" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Blended Moderate S Acc</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
+      <c r="B326" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW5B06</t>
         </is>
@@ -5945,12 +5945,12 @@
       </c>
     </row>
     <row r="327" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A327" t="inlineStr">
+      <c r="A327" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Blended Moderate S Inc</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
+      <c r="B327" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW5986</t>
         </is>
@@ -5962,12 +5962,12 @@
       </c>
     </row>
     <row r="328" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A328" t="inlineStr">
+      <c r="A328" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Blended Progressive A Acc</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
+      <c r="B328" s="6" t="inlineStr">
         <is>
           <t>GB00B8JY5364</t>
         </is>
@@ -5979,12 +5979,12 @@
       </c>
     </row>
     <row r="329" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A329" t="inlineStr">
+      <c r="A329" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Blended Progressive S Acc</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
+      <c r="B329" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW5J81</t>
         </is>
@@ -5996,12 +5996,12 @@
       </c>
     </row>
     <row r="330" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A330" t="inlineStr">
+      <c r="A330" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Blended Reserve S Acc</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
+      <c r="B330" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW5D20</t>
         </is>
@@ -6013,12 +6013,12 @@
       </c>
     </row>
     <row r="331" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A331" t="inlineStr">
+      <c r="A331" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Blended Reserve S Inc</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
+      <c r="B331" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW5C13</t>
         </is>
@@ -6030,12 +6030,12 @@
       </c>
     </row>
     <row r="332" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A332" t="inlineStr">
+      <c r="A332" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Adventurous D Acc</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
+      <c r="B332" s="6" t="inlineStr">
         <is>
           <t>GB00BNGNDL53</t>
         </is>
@@ -6047,12 +6047,12 @@
       </c>
     </row>
     <row r="333" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A333" t="inlineStr">
+      <c r="A333" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Adventurous S Acc</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
+      <c r="B333" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW4Y67</t>
         </is>
@@ -6064,12 +6064,12 @@
       </c>
     </row>
     <row r="334" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A334" t="inlineStr">
+      <c r="A334" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Growth D Acc</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
+      <c r="B334" s="6" t="inlineStr">
         <is>
           <t>GB00BNGNDK47</t>
         </is>
@@ -6081,12 +6081,12 @@
       </c>
     </row>
     <row r="335" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A335" t="inlineStr">
+      <c r="A335" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Growth S Acc</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
+      <c r="B335" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW4X50</t>
         </is>
@@ -6098,12 +6098,12 @@
       </c>
     </row>
     <row r="336" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A336" t="inlineStr">
+      <c r="A336" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Intermediate D Acc</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
+      <c r="B336" s="6" t="inlineStr">
         <is>
           <t>GB00BNGNDH18</t>
         </is>
@@ -6115,12 +6115,12 @@
       </c>
     </row>
     <row r="337" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A337" t="inlineStr">
+      <c r="A337" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Intermediate S Acc</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B337" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW4V37</t>
         </is>
@@ -6132,12 +6132,12 @@
       </c>
     </row>
     <row r="338" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A338" t="inlineStr">
+      <c r="A338" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Moderate D Acc</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr">
+      <c r="B338" s="6" t="inlineStr">
         <is>
           <t>GB00BNGNDG01</t>
         </is>
@@ -6149,12 +6149,12 @@
       </c>
     </row>
     <row r="339" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A339" t="inlineStr">
+      <c r="A339" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Moderate D Inc</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
+      <c r="B339" s="6" t="inlineStr">
         <is>
           <t>GB00BWWCYY97</t>
         </is>
@@ -6166,12 +6166,12 @@
       </c>
     </row>
     <row r="340" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A340" t="inlineStr">
+      <c r="A340" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Moderate S Acc</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
+      <c r="B340" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW4T15</t>
         </is>
@@ -6183,12 +6183,12 @@
       </c>
     </row>
     <row r="341" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A341" t="inlineStr">
+      <c r="A341" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Moderate S Inc</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
+      <c r="B341" s="6" t="inlineStr">
         <is>
           <t>GB00BWWCYX80</t>
         </is>
@@ -6200,12 +6200,12 @@
       </c>
     </row>
     <row r="342" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A342" t="inlineStr">
+      <c r="A342" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Progressive D Acc</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
+      <c r="B342" s="6" t="inlineStr">
         <is>
           <t>GB00BNGNDJ32</t>
         </is>
@@ -6217,12 +6217,12 @@
       </c>
     </row>
     <row r="343" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A343" t="inlineStr">
+      <c r="A343" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Progressive S Acc</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
+      <c r="B343" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW4W44</t>
         </is>
@@ -6234,12 +6234,12 @@
       </c>
     </row>
     <row r="344" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A344" t="inlineStr">
+      <c r="A344" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Prudent D Acc</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
+      <c r="B344" s="6" t="inlineStr">
         <is>
           <t>GB00BNGNDM60</t>
         </is>
@@ -6251,12 +6251,12 @@
       </c>
     </row>
     <row r="345" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A345" t="inlineStr">
+      <c r="A345" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Prudent S Acc</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
+      <c r="B345" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW4Z74</t>
         </is>
@@ -6268,12 +6268,12 @@
       </c>
     </row>
     <row r="346" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A346" t="inlineStr">
+      <c r="A346" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Reserve D Acc</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
+      <c r="B346" s="6" t="inlineStr">
         <is>
           <t>GB00BNGNDF93</t>
         </is>
@@ -6285,12 +6285,12 @@
       </c>
     </row>
     <row r="347" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A347" t="inlineStr">
+      <c r="A347" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Dynamic Passive Reserve S Acc</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
+      <c r="B347" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW4S08</t>
         </is>
@@ -6302,12 +6302,12 @@
       </c>
     </row>
     <row r="348" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A348" t="inlineStr">
+      <c r="A348" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Explorer 100 A Acc</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
+      <c r="B348" s="6" t="inlineStr">
         <is>
           <t>GB00B6ZRLF91</t>
         </is>
@@ -6319,12 +6319,12 @@
       </c>
     </row>
     <row r="349" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A349" t="inlineStr">
+      <c r="A349" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Explorer 100 S Acc</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
+      <c r="B349" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW6844</t>
         </is>
@@ -6336,12 +6336,12 @@
       </c>
     </row>
     <row r="350" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A350" t="inlineStr">
+      <c r="A350" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Explorer 35 S Acc</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
+      <c r="B350" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW6N92</t>
         </is>
@@ -6353,12 +6353,12 @@
       </c>
     </row>
     <row r="351" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A351" t="inlineStr">
+      <c r="A351" s="6" t="inlineStr">
         <is>
           <t>Liontrust MA Explorer 35 S Inc</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
+      <c r="B351" s="6" t="inlineStr">
         <is>
           <t>GB00BCZW6M85</t>
         </is>
@@ -6370,12 +6370,12 @@
       </c>
     </row>
     <row r="352" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A352" t="inlineStr">
+      <c r="A352" s="6" t="inlineStr">
         <is>
           <t>MI Verbatim Portfolio 4 B Acc</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
+      <c r="B352" s="6" t="inlineStr">
         <is>
           <t>GB00B3P42N43</t>
         </is>
@@ -6387,12 +6387,12 @@
       </c>
     </row>
     <row r="353" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A353" t="inlineStr">
+      <c r="A353" s="6" t="inlineStr">
         <is>
           <t>MI Verbatim Portfolio 5 Growth B Acc</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B353" s="6" t="inlineStr">
         <is>
           <t>GB00B3P2HB11</t>
         </is>
@@ -6404,12 +6404,12 @@
       </c>
     </row>
     <row r="354" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A354" t="inlineStr">
+      <c r="A354" s="6" t="inlineStr">
         <is>
           <t>MI Verbatim Portfolio 6 B Acc</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
+      <c r="B354" s="6" t="inlineStr">
         <is>
           <t>GB00B3MPJG29</t>
         </is>
@@ -6421,12 +6421,12 @@
       </c>
     </row>
     <row r="355" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A355" t="inlineStr">
+      <c r="A355" s="6" t="inlineStr">
         <is>
           <t>MI Verbatim Portfolio 7 B Acc</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
+      <c r="B355" s="6" t="inlineStr">
         <is>
           <t>GB00B3PVM139</t>
         </is>
@@ -6438,12 +6438,12 @@
       </c>
     </row>
     <row r="356" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A356" t="inlineStr">
+      <c r="A356" s="6" t="inlineStr">
         <is>
           <t>Ministry Of Justice Equity Index Tracker Distribution</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
+      <c r="B356" s="6" t="inlineStr">
         <is>
           <t>GB0003559480</t>
         </is>
@@ -6455,12 +6455,12 @@
       </c>
     </row>
     <row r="357" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A357" t="inlineStr">
+      <c r="A357" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Convertibles Global DH GBP</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
+      <c r="B357" s="6" t="inlineStr">
         <is>
           <t>LU1060797062</t>
         </is>
@@ -6472,12 +6472,12 @@
       </c>
     </row>
     <row r="358" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A358" t="inlineStr">
+      <c r="A358" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Discovery Europe D Cap GBP</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
+      <c r="B358" s="6" t="inlineStr">
         <is>
           <t>LU1308311924</t>
         </is>
@@ -6489,12 +6489,12 @@
       </c>
     </row>
     <row r="359" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A359" t="inlineStr">
+      <c r="A359" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Discovery Europe Ex-UK D Cap GBP</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
+      <c r="B359" s="6" t="inlineStr">
         <is>
           <t>LU1308314605</t>
         </is>
@@ -6506,12 +6506,12 @@
       </c>
     </row>
     <row r="360" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A360" t="inlineStr">
+      <c r="A360" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Discovery Europe Ex-UK DH Cap GBP</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr">
+      <c r="B360" s="6" t="inlineStr">
         <is>
           <t>LU1308315248</t>
         </is>
@@ -6523,12 +6523,12 @@
       </c>
     </row>
     <row r="361" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A361" t="inlineStr">
+      <c r="A361" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Discovery Europe Ex-UK G Acc GBP</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
+      <c r="B361" s="6" t="inlineStr">
         <is>
           <t>LU3037638569</t>
         </is>
@@ -6540,12 +6540,12 @@
       </c>
     </row>
     <row r="362" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A362" t="inlineStr">
+      <c r="A362" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Discovery Europe G Acc GBP</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
+      <c r="B362" s="6" t="inlineStr">
         <is>
           <t>LU3037638643</t>
         </is>
@@ -6557,12 +6557,12 @@
       </c>
     </row>
     <row r="363" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A363" t="inlineStr">
+      <c r="A363" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Global Dividend D Cap GBP</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
+      <c r="B363" s="6" t="inlineStr">
         <is>
           <t>LU1064860858</t>
         </is>
@@ -6574,12 +6574,12 @@
       </c>
     </row>
     <row r="364" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A364" t="inlineStr">
+      <c r="A364" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Global Dividend G Acc GBP</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr">
+      <c r="B364" s="6" t="inlineStr">
         <is>
           <t>LU3037638726</t>
         </is>
@@ -6591,12 +6591,12 @@
       </c>
     </row>
     <row r="365" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A365" t="inlineStr">
+      <c r="A365" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Global Emerging Market Bond DH Acc GBP</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr">
+      <c r="B365" s="6" t="inlineStr">
         <is>
           <t>LU1705559372</t>
         </is>
@@ -6608,12 +6608,12 @@
       </c>
     </row>
     <row r="366" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A366" t="inlineStr">
+      <c r="A366" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Global Focus D GBP</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B366" s="6" t="inlineStr">
         <is>
           <t>LU1203833618</t>
         </is>
@@ -6625,12 +6625,12 @@
       </c>
     </row>
     <row r="367" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A367" t="inlineStr">
+      <c r="A367" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Global Focus G Acc GBP</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr">
+      <c r="B367" s="6" t="inlineStr">
         <is>
           <t>LU3037638999</t>
         </is>
@@ -6642,12 +6642,12 @@
       </c>
     </row>
     <row r="368" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A368" t="inlineStr">
+      <c r="A368" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Global High Yield Bonds DH Cap GBP</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B368" s="6" t="inlineStr">
         <is>
           <t>LU0972917131</t>
         </is>
@@ -6659,12 +6659,12 @@
       </c>
     </row>
     <row r="369" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A369" t="inlineStr">
+      <c r="A369" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Global High Yield Bonds DH Dist GBP</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
+      <c r="B369" s="6" t="inlineStr">
         <is>
           <t>LU0972917214</t>
         </is>
@@ -6676,12 +6676,12 @@
       </c>
     </row>
     <row r="370" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A370" t="inlineStr">
+      <c r="A370" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Global Short Duration DH Dis GBP</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
+      <c r="B370" s="6" t="inlineStr">
         <is>
           <t>LU1308309274</t>
         </is>
@@ -6693,12 +6693,12 @@
       </c>
     </row>
     <row r="371" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A371" t="inlineStr">
+      <c r="A371" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Global Strategic Bond DH Cap GBP</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
+      <c r="B371" s="6" t="inlineStr">
         <is>
           <t>LU0972400609</t>
         </is>
@@ -6710,12 +6710,12 @@
       </c>
     </row>
     <row r="372" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A372" t="inlineStr">
+      <c r="A372" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Global Strategic Bond DH Dist GBP</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
+      <c r="B372" s="6" t="inlineStr">
         <is>
           <t>LU0972400948</t>
         </is>
@@ -6727,12 +6727,12 @@
       </c>
     </row>
     <row r="373" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A373" t="inlineStr">
+      <c r="A373" s="6" t="inlineStr">
         <is>
           <t>Mirabaud Global Strategic Bond GH Acc GBP</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
+      <c r="B373" s="6" t="inlineStr">
         <is>
           <t>LU3037639021</t>
         </is>
@@ -6744,12 +6744,12 @@
       </c>
     </row>
     <row r="374" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A374" t="inlineStr">
+      <c r="A374" s="6" t="inlineStr">
         <is>
           <t>Mirae Asset ESG Asia Great Consumer Equity R GBP</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr">
+      <c r="B374" s="6" t="inlineStr">
         <is>
           <t>LU0853239118</t>
         </is>
@@ -6761,12 +6761,12 @@
       </c>
     </row>
     <row r="375" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A375" t="inlineStr">
+      <c r="A375" s="6" t="inlineStr">
         <is>
           <t>Mirae Asset ESG Asia Sector Leader Equity R GBP</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr">
+      <c r="B375" s="6" t="inlineStr">
         <is>
           <t>LU1061547755</t>
         </is>
@@ -6778,12 +6778,12 @@
       </c>
     </row>
     <row r="376" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A376" t="inlineStr">
+      <c r="A376" s="6" t="inlineStr">
         <is>
           <t>Mirae Asset India Sector Leader Equity R GBP</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr">
+      <c r="B376" s="6" t="inlineStr">
         <is>
           <t>LU0853239548</t>
         </is>
@@ -6795,12 +6795,12 @@
       </c>
     </row>
     <row r="377" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A377" t="inlineStr">
+      <c r="A377" s="6" t="inlineStr">
         <is>
           <t>Mirova Euro Short Term Sustainable Bond N/A H Cap GBP</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr">
+      <c r="B377" s="6" t="inlineStr">
         <is>
           <t>LU2584248244</t>
         </is>
@@ -6812,12 +6812,12 @@
       </c>
     </row>
     <row r="378" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A378" t="inlineStr">
+      <c r="A378" s="6" t="inlineStr">
         <is>
           <t>MontLake 1OAK Multi Asset 80 UCITs A GBP</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr">
+      <c r="B378" s="6" t="inlineStr">
         <is>
           <t>IE00BMW4T172</t>
         </is>
@@ -6829,12 +6829,12 @@
       </c>
     </row>
     <row r="379" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A379" t="inlineStr">
+      <c r="A379" s="6" t="inlineStr">
         <is>
           <t>MontLake Collidr Adaptive Global Equity UCITS A GBP</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
+      <c r="B379" s="6" t="inlineStr">
         <is>
           <t>IE00BZ1NRQ72</t>
         </is>
@@ -6846,12 +6846,12 @@
       </c>
     </row>
     <row r="380" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A380" t="inlineStr">
+      <c r="A380" s="6" t="inlineStr">
         <is>
           <t>MontLake Collidr Adaptive Global Equity UCITS B GBP</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr">
+      <c r="B380" s="6" t="inlineStr">
         <is>
           <t>IE00BZ1NS316</t>
         </is>
@@ -6863,12 +6863,12 @@
       </c>
     </row>
     <row r="381" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A381" t="inlineStr">
+      <c r="A381" s="6" t="inlineStr">
         <is>
           <t>MontLake Cooper Creek Partners North America Lng Shrt Eqty UCT Inst Pld GBP</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr">
+      <c r="B381" s="6" t="inlineStr">
         <is>
           <t>IE00BG08P774</t>
         </is>
@@ -6880,12 +6880,12 @@
       </c>
     </row>
     <row r="382" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A382" t="inlineStr">
+      <c r="A382" s="6" t="inlineStr">
         <is>
           <t>MontLake DUNN WMA Institutional UCITS Institutional Pooled A GBP</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr">
+      <c r="B382" s="6" t="inlineStr">
         <is>
           <t>IE00BYZJ5H19</t>
         </is>
@@ -6897,12 +6897,12 @@
       </c>
     </row>
     <row r="383" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A383" t="inlineStr">
+      <c r="A383" s="6" t="inlineStr">
         <is>
           <t>MontLake DUNN WMA Institutional UCITS Retail Pooled Class GBP</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
+      <c r="B383" s="6" t="inlineStr">
         <is>
           <t>IE00B6R2TF82</t>
         </is>
@@ -6914,12 +6914,12 @@
       </c>
     </row>
     <row r="384" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A384" t="inlineStr">
+      <c r="A384" s="6" t="inlineStr">
         <is>
           <t>MontLake Tosca Micro Cap UCITS Fund Institutional Pooled GBP</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr">
+      <c r="B384" s="6" t="inlineStr">
         <is>
           <t>IE00B3RTD232</t>
         </is>
@@ -6931,12 +6931,12 @@
       </c>
     </row>
     <row r="385" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A385" t="inlineStr">
+      <c r="A385" s="6" t="inlineStr">
         <is>
           <t>Montanaro Better World Dist GBP</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr">
+      <c r="B385" s="6" t="inlineStr">
         <is>
           <t>IE00BYWFFF02</t>
         </is>
@@ -6948,12 +6948,12 @@
       </c>
     </row>
     <row r="386" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A386" t="inlineStr">
+      <c r="A386" s="6" t="inlineStr">
         <is>
           <t>Montanaro European Income Acc GBP</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr">
+      <c r="B386" s="6" t="inlineStr">
         <is>
           <t>IE00BFFK9M41</t>
         </is>
@@ -6965,12 +6965,12 @@
       </c>
     </row>
     <row r="387" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A387" t="inlineStr">
+      <c r="A387" s="6" t="inlineStr">
         <is>
           <t>Montanaro European Income Inc GBP</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr">
+      <c r="B387" s="6" t="inlineStr">
         <is>
           <t>IE00B3Q8KY24</t>
         </is>
@@ -6982,12 +6982,12 @@
       </c>
     </row>
     <row r="388" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A388" t="inlineStr">
+      <c r="A388" s="6" t="inlineStr">
         <is>
           <t>Montanaro European Smaller Companies Inst Inc GBP</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
+      <c r="B388" s="6" t="inlineStr">
         <is>
           <t>IE00B3V9KZ14</t>
         </is>
@@ -6999,12 +6999,12 @@
       </c>
     </row>
     <row r="389" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A389" t="inlineStr">
+      <c r="A389" s="6" t="inlineStr">
         <is>
           <t>Montanaro UK Income Acc GBP</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
+      <c r="B389" s="6" t="inlineStr">
         <is>
           <t>IE00BFFK9L34</t>
         </is>
@@ -7016,12 +7016,12 @@
       </c>
     </row>
     <row r="390" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A390" t="inlineStr">
+      <c r="A390" s="6" t="inlineStr">
         <is>
           <t>Montanaro UK Income GBP</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
+      <c r="B390" s="6" t="inlineStr">
         <is>
           <t>IE00BYSRYZ31</t>
         </is>
@@ -7033,12 +7033,12 @@
       </c>
     </row>
     <row r="391" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A391" t="inlineStr">
+      <c r="A391" s="6" t="inlineStr">
         <is>
           <t>Montanaro UK Income Seed GBP</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
+      <c r="B391" s="6" t="inlineStr">
         <is>
           <t>IE00B1FZRT49</t>
         </is>
@@ -7050,12 +7050,12 @@
       </c>
     </row>
     <row r="392" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A392" t="inlineStr">
+      <c r="A392" s="6" t="inlineStr">
         <is>
           <t>Morant Wright Fuji Yield Hedged Inc GBP</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
+      <c r="B392" s="6" t="inlineStr">
         <is>
           <t>IE00BQT49F20</t>
         </is>
@@ -7067,12 +7067,12 @@
       </c>
     </row>
     <row r="393" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A393" t="inlineStr">
+      <c r="A393" s="6" t="inlineStr">
         <is>
           <t>Morant Wright Fuji Yield Unhedged Inc GBP</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr">
+      <c r="B393" s="6" t="inlineStr">
         <is>
           <t>IE00BYWNV678</t>
         </is>
@@ -7084,12 +7084,12 @@
       </c>
     </row>
     <row r="394" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A394" t="inlineStr">
+      <c r="A394" s="6" t="inlineStr">
         <is>
           <t>Morant Wright Sakura Unhedged Inc GBP</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
+      <c r="B394" s="6" t="inlineStr">
         <is>
           <t>IE00BYWNV348</t>
         </is>
@@ -7101,12 +7101,12 @@
       </c>
     </row>
     <row r="395" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A395" t="inlineStr">
+      <c r="A395" s="6" t="inlineStr">
         <is>
           <t>Morg Stnly Global Brands ZHR GBP</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
+      <c r="B395" s="6" t="inlineStr">
         <is>
           <t>LU1418832595</t>
         </is>
@@ -7118,12 +7118,12 @@
       </c>
     </row>
     <row r="396" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A396" t="inlineStr">
+      <c r="A396" s="6" t="inlineStr">
         <is>
           <t>Morgan Stanley Calvert Fixed Income Opportunities F Acc GBP</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr">
+      <c r="B396" s="6" t="inlineStr">
         <is>
           <t>GB00BNKVPG43</t>
         </is>
@@ -7135,12 +7135,12 @@
       </c>
     </row>
     <row r="397" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A397" t="inlineStr">
+      <c r="A397" s="6" t="inlineStr">
         <is>
           <t>Morgan Stanley Calvert Fixed Income Opportunities F Inc GBP</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
+      <c r="B397" s="6" t="inlineStr">
         <is>
           <t>GB00BNKVPH59</t>
         </is>
@@ -7152,12 +7152,12 @@
       </c>
     </row>
     <row r="398" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A398" t="inlineStr">
+      <c r="A398" s="6" t="inlineStr">
         <is>
           <t>Morgan Stanley Global Brands Equity Income I Acc GBP</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
+      <c r="B398" s="6" t="inlineStr">
         <is>
           <t>GB00BZ4CG420</t>
         </is>
@@ -7169,12 +7169,12 @@
       </c>
     </row>
     <row r="399" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A399" t="inlineStr">
+      <c r="A399" s="6" t="inlineStr">
         <is>
           <t>Morgan Stanley Global Brands Equity Income I Inc GBP</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
+      <c r="B399" s="6" t="inlineStr">
         <is>
           <t>GB00BZ4CG537</t>
         </is>
@@ -7186,12 +7186,12 @@
       </c>
     </row>
     <row r="400" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A400" t="inlineStr">
+      <c r="A400" s="6" t="inlineStr">
         <is>
           <t>Morgan Stanley Global Brands I (Portfolio Hedged) Acc</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
+      <c r="B400" s="6" t="inlineStr">
         <is>
           <t>GB00BJNQ8J24</t>
         </is>
@@ -7203,12 +7203,12 @@
       </c>
     </row>
     <row r="401" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A401" t="inlineStr">
+      <c r="A401" s="6" t="inlineStr">
         <is>
           <t>Morgan Stanley Global Brands I (Portfolio Hedged) Inc</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
+      <c r="B401" s="6" t="inlineStr">
         <is>
           <t>GB00BJNQ8K39</t>
         </is>
@@ -7220,12 +7220,12 @@
       </c>
     </row>
     <row r="402" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A402" t="inlineStr">
+      <c r="A402" s="6" t="inlineStr">
         <is>
           <t>POLEN CAPITAL GLOBAL GROWTH J3 Cap GBP</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
+      <c r="B402" s="6" t="inlineStr">
         <is>
           <t>LU2110862385</t>
         </is>
@@ -7237,12 +7237,12 @@
       </c>
     </row>
     <row r="403" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A403" t="inlineStr">
+      <c r="A403" s="6" t="inlineStr">
         <is>
           <t>POLEN CAPITAL GLOBAL GROWTH J3 Dis GBP</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
+      <c r="B403" s="6" t="inlineStr">
         <is>
           <t>LU2110862468</t>
         </is>
@@ -7254,12 +7254,12 @@
       </c>
     </row>
     <row r="404" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A404" t="inlineStr">
+      <c r="A404" s="6" t="inlineStr">
         <is>
           <t>Polar Capital Healthcare Blue Chip S Inc GBP</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
+      <c r="B404" s="6" t="inlineStr">
         <is>
           <t>IE00BPRBXY58</t>
         </is>
@@ -7271,12 +7271,12 @@
       </c>
     </row>
     <row r="405" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A405" t="inlineStr">
+      <c r="A405" s="6" t="inlineStr">
         <is>
           <t>Polar Capital Healthcare Discovery I Acc GBP</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
+      <c r="B405" s="6" t="inlineStr">
         <is>
           <t>IE00BJXT2B13</t>
         </is>
@@ -7288,12 +7288,12 @@
       </c>
     </row>
     <row r="406" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A406" t="inlineStr">
+      <c r="A406" s="6" t="inlineStr">
         <is>
           <t>Polar Capital Healthcare Opportunities I Acc EUR</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
+      <c r="B406" s="6" t="inlineStr">
         <is>
           <t>IE00BF12WY77</t>
         </is>
@@ -7305,12 +7305,12 @@
       </c>
     </row>
     <row r="407" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A407" t="inlineStr">
+      <c r="A407" s="6" t="inlineStr">
         <is>
           <t>Polar Capital Healthcare Opportunities I GBP</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
+      <c r="B407" s="6" t="inlineStr">
         <is>
           <t>IE00B3NLDF60</t>
         </is>
@@ -7322,12 +7322,12 @@
       </c>
     </row>
     <row r="408" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A408" t="inlineStr">
+      <c r="A408" s="6" t="inlineStr">
         <is>
           <t>Polar Capital Japan Value S Hedged Inc GBP</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
+      <c r="B408" s="6" t="inlineStr">
         <is>
           <t>IE00B8C0M523</t>
         </is>
@@ -7339,12 +7339,12 @@
       </c>
     </row>
     <row r="409" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A409" t="inlineStr">
+      <c r="A409" s="6" t="inlineStr">
         <is>
           <t>Polar Capital Japan Value S Inc GBP</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
+      <c r="B409" s="6" t="inlineStr">
         <is>
           <t>IE00B6TBKM73</t>
         </is>
@@ -7356,12 +7356,12 @@
       </c>
     </row>
     <row r="410" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A410" t="inlineStr">
+      <c r="A410" s="6" t="inlineStr">
         <is>
           <t>Polar Capital North American S GBP</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr">
+      <c r="B410" s="6" t="inlineStr">
         <is>
           <t>IE00B713C335</t>
         </is>
@@ -7373,12 +7373,12 @@
       </c>
     </row>
     <row r="411" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A411" t="inlineStr">
+      <c r="A411" s="6" t="inlineStr">
         <is>
           <t>Polar Capital North American S Hedged GBP</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr">
+      <c r="B411" s="6" t="inlineStr">
         <is>
           <t>IE00B7136W05</t>
         </is>
@@ -7390,12 +7390,12 @@
       </c>
     </row>
     <row r="412" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A412" t="inlineStr">
+      <c r="A412" s="6" t="inlineStr">
         <is>
           <t>Polar Capital Smart Energy I Acc GBP</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr">
+      <c r="B412" s="6" t="inlineStr">
         <is>
           <t>IE000GWLH680</t>
         </is>
@@ -7407,12 +7407,12 @@
       </c>
     </row>
     <row r="413" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A413" t="inlineStr">
+      <c r="A413" s="6" t="inlineStr">
         <is>
           <t>Polar Capital UK Value Opportunities I Acc GBP</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr">
+      <c r="B413" s="6" t="inlineStr">
         <is>
           <t>IE00BD81XX91</t>
         </is>
@@ -7424,12 +7424,12 @@
       </c>
     </row>
     <row r="414" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A414" t="inlineStr">
+      <c r="A414" s="6" t="inlineStr">
         <is>
           <t>Polar Capital UK Value Opportunities I Inc GBP</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
+      <c r="B414" s="6" t="inlineStr">
         <is>
           <t>IE00BD81XW84</t>
         </is>
@@ -7441,12 +7441,12 @@
       </c>
     </row>
     <row r="415" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A415" t="inlineStr">
+      <c r="A415" s="6" t="inlineStr">
         <is>
           <t>Polar Emerging Market Stars I GBP</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
+      <c r="B415" s="6" t="inlineStr">
         <is>
           <t>IE00BFMFDG40</t>
         </is>
@@ -7458,12 +7458,12 @@
       </c>
     </row>
     <row r="416" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A416" t="inlineStr">
+      <c r="A416" s="6" t="inlineStr">
         <is>
           <t>Polen Capital 5Perspectives U.S. Small Inst USD</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr">
+      <c r="B416" s="6" t="inlineStr">
         <is>
           <t>IE00BYWHB920</t>
         </is>
@@ -7475,12 +7475,12 @@
       </c>
     </row>
     <row r="417" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A417" t="inlineStr">
+      <c r="A417" s="6" t="inlineStr">
         <is>
           <t>Polen Capital Focus US Growth Inst GBP</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
+      <c r="B417" s="6" t="inlineStr">
         <is>
           <t>IE00B7WMPB80</t>
         </is>
@@ -7492,12 +7492,12 @@
       </c>
     </row>
     <row r="418" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A418" t="inlineStr">
+      <c r="A418" s="6" t="inlineStr">
         <is>
           <t>Polen Capital Focus US Growth Inst USD</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
+      <c r="B418" s="6" t="inlineStr">
         <is>
           <t>IE00B8DDPY03</t>
         </is>
@@ -7509,12 +7509,12 @@
       </c>
     </row>
     <row r="419" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A419" t="inlineStr">
+      <c r="A419" s="6" t="inlineStr">
         <is>
           <t>Polen Capital Focus US Growth Inst Unhedged</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr">
+      <c r="B419" s="6" t="inlineStr">
         <is>
           <t>IE00BYYP0W07</t>
         </is>
@@ -7526,12 +7526,12 @@
       </c>
     </row>
     <row r="420" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A420" t="inlineStr">
+      <c r="A420" s="6" t="inlineStr">
         <is>
           <t>Practical Investment Acc</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
+      <c r="B420" s="6" t="inlineStr">
         <is>
           <t>GB0006982671</t>
         </is>
@@ -7543,12 +7543,12 @@
       </c>
     </row>
     <row r="421" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A421" t="inlineStr">
+      <c r="A421" s="6" t="inlineStr">
         <is>
           <t>Practical Investment Inc</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
+      <c r="B421" s="6" t="inlineStr">
         <is>
           <t>GB0006982457</t>
         </is>
@@ -7560,12 +7560,12 @@
       </c>
     </row>
     <row r="422" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A422" t="inlineStr">
+      <c r="A422" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Alternative Investments C Acc GBP</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr">
+      <c r="B422" s="6" t="inlineStr">
         <is>
           <t>GB00BTHH0518</t>
         </is>
@@ -7577,12 +7577,12 @@
       </c>
     </row>
     <row r="423" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A423" t="inlineStr">
+      <c r="A423" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Alternative Investments C Inc GBP</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
+      <c r="B423" s="6" t="inlineStr">
         <is>
           <t>GB00B832BD89</t>
         </is>
@@ -7594,12 +7594,12 @@
       </c>
     </row>
     <row r="424" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A424" t="inlineStr">
+      <c r="A424" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Cautious Monthly Income B Acc GBP</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr">
+      <c r="B424" s="6" t="inlineStr">
         <is>
           <t>GB00B7T13474</t>
         </is>
@@ -7611,12 +7611,12 @@
       </c>
     </row>
     <row r="425" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A425" t="inlineStr">
+      <c r="A425" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Cautious Monthly Income B Inc GBP</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
+      <c r="B425" s="6" t="inlineStr">
         <is>
           <t>GB00B79QBF93</t>
         </is>
@@ -7628,12 +7628,12 @@
       </c>
     </row>
     <row r="426" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A426" t="inlineStr">
+      <c r="A426" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Cautious Multi Asset B Acc GBP</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
+      <c r="B426" s="6" t="inlineStr">
         <is>
           <t>GB00B0W1V856</t>
         </is>
@@ -7645,12 +7645,12 @@
       </c>
     </row>
     <row r="427" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A427" t="inlineStr">
+      <c r="A427" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Corporate Bond Monthly Income C Acc GBP</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr">
+      <c r="B427" s="6" t="inlineStr">
         <is>
           <t>GB00BMX6FH03</t>
         </is>
@@ -7662,12 +7662,12 @@
       </c>
     </row>
     <row r="428" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A428" t="inlineStr">
+      <c r="A428" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Corporate Bond Monthly Income C Inc GBP</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
+      <c r="B428" s="6" t="inlineStr">
         <is>
           <t>GB0003895496</t>
         </is>
@@ -7679,12 +7679,12 @@
       </c>
     </row>
     <row r="429" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A429" t="inlineStr">
+      <c r="A429" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Defensive Multi Asset B Acc GBP</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr">
+      <c r="B429" s="6" t="inlineStr">
         <is>
           <t>GB00B0525B66</t>
         </is>
@@ -7696,12 +7696,12 @@
       </c>
     </row>
     <row r="430" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A430" t="inlineStr">
+      <c r="A430" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Defensive Multi Asset B Inc GBP</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr">
+      <c r="B430" s="6" t="inlineStr">
         <is>
           <t>GB00BMYBW060</t>
         </is>
@@ -7713,12 +7713,12 @@
       </c>
     </row>
     <row r="431" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A431" t="inlineStr">
+      <c r="A431" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Diversified Balanced Growth D Acc GBP</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr">
+      <c r="B431" s="6" t="inlineStr">
         <is>
           <t>GB00BMQ5MM85</t>
         </is>
@@ -7730,12 +7730,12 @@
       </c>
     </row>
     <row r="432" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A432" t="inlineStr">
+      <c r="A432" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Diversified Balanced Growth D Inc GBP</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr">
+      <c r="B432" s="6" t="inlineStr">
         <is>
           <t>GB00BHNWGP88</t>
         </is>
@@ -7747,12 +7747,12 @@
       </c>
     </row>
     <row r="433" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A433" t="inlineStr">
+      <c r="A433" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Diversified Cautious Growth D Acc GBP</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr">
+      <c r="B433" s="6" t="inlineStr">
         <is>
           <t>GB00BMQ5MN92</t>
         </is>
@@ -7764,12 +7764,12 @@
       </c>
     </row>
     <row r="434" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A434" t="inlineStr">
+      <c r="A434" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Diversified Cautious Growth D Inc GBP</t>
         </is>
       </c>
-      <c r="B434" t="inlineStr">
+      <c r="B434" s="6" t="inlineStr">
         <is>
           <t>GB00BHNZ2P92</t>
         </is>
@@ -7781,12 +7781,12 @@
       </c>
     </row>
     <row r="435" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A435" t="inlineStr">
+      <c r="A435" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Diversified Dynamic Growth D Acc GBP</t>
         </is>
       </c>
-      <c r="B435" t="inlineStr">
+      <c r="B435" s="6" t="inlineStr">
         <is>
           <t>GB00BMQ5ML78</t>
         </is>
@@ -7798,12 +7798,12 @@
       </c>
     </row>
     <row r="436" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A436" t="inlineStr">
+      <c r="A436" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Diversified Dynamic Growth D Inc GBP</t>
         </is>
       </c>
-      <c r="B436" t="inlineStr">
+      <c r="B436" s="6" t="inlineStr">
         <is>
           <t>GB00BHNWH995</t>
         </is>
@@ -7815,12 +7815,12 @@
       </c>
     </row>
     <row r="437" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A437" t="inlineStr">
+      <c r="A437" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Diversified Growth D Acc GBP</t>
         </is>
       </c>
-      <c r="B437" t="inlineStr">
+      <c r="B437" s="6" t="inlineStr">
         <is>
           <t>GB00BMQ5L211</t>
         </is>
@@ -7832,12 +7832,12 @@
       </c>
     </row>
     <row r="438" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A438" t="inlineStr">
+      <c r="A438" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Diversified Growth D Inc GBP</t>
         </is>
       </c>
-      <c r="B438" t="inlineStr">
+      <c r="B438" s="6" t="inlineStr">
         <is>
           <t>GB00B8BJV423</t>
         </is>
@@ -7849,12 +7849,12 @@
       </c>
     </row>
     <row r="439" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A439" t="inlineStr">
+      <c r="A439" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Diversified Income D Acc GBP</t>
         </is>
       </c>
-      <c r="B439" t="inlineStr">
+      <c r="B439" s="6" t="inlineStr">
         <is>
           <t>GB00BMQ5MK61</t>
         </is>
@@ -7866,12 +7866,12 @@
       </c>
     </row>
     <row r="440" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A440" t="inlineStr">
+      <c r="A440" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Diversified Income D Inc GBP</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
+      <c r="B440" s="6" t="inlineStr">
         <is>
           <t>GB00BYPDV970</t>
         </is>
@@ -7883,12 +7883,12 @@
       </c>
     </row>
     <row r="441" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A441" t="inlineStr">
+      <c r="A441" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Diversified Responsible Growth D Acc GBP</t>
         </is>
       </c>
-      <c r="B441" t="inlineStr">
+      <c r="B441" s="6" t="inlineStr">
         <is>
           <t>GB00BF1CW039</t>
         </is>
@@ -7900,12 +7900,12 @@
       </c>
     </row>
     <row r="442" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A442" t="inlineStr">
+      <c r="A442" s="6" t="inlineStr">
         <is>
           <t>Premier Miton European Opportunities B Inc GBP</t>
         </is>
       </c>
-      <c r="B442" t="inlineStr">
+      <c r="B442" s="6" t="inlineStr">
         <is>
           <t>GB00BMCC2016</t>
         </is>
@@ -7917,12 +7917,12 @@
       </c>
     </row>
     <row r="443" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A443" t="inlineStr">
+      <c r="A443" s="6" t="inlineStr">
         <is>
           <t>Premier Miton European Opportunities F Acc GBP</t>
         </is>
       </c>
-      <c r="B443" t="inlineStr">
+      <c r="B443" s="6" t="inlineStr">
         <is>
           <t>GB00BYZ55N51</t>
         </is>
@@ -7934,12 +7934,12 @@
       </c>
     </row>
     <row r="444" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A444" t="inlineStr">
+      <c r="A444" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Global Infrastructure Income B Acc GBP</t>
         </is>
       </c>
-      <c r="B444" t="inlineStr">
+      <c r="B444" s="6" t="inlineStr">
         <is>
           <t>GB00BD3H9L21</t>
         </is>
@@ -7951,12 +7951,12 @@
       </c>
     </row>
     <row r="445" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A445" t="inlineStr">
+      <c r="A445" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Global Infrastructure Income B Inc GBP</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr">
+      <c r="B445" s="6" t="inlineStr">
         <is>
           <t>GB00BD3H9M38</t>
         </is>
@@ -7968,12 +7968,12 @@
       </c>
     </row>
     <row r="446" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A446" t="inlineStr">
+      <c r="A446" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Global Sustainable Growth C Acc GBP</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr">
+      <c r="B446" s="6" t="inlineStr">
         <is>
           <t>GB00B6740K61</t>
         </is>
@@ -7985,12 +7985,12 @@
       </c>
     </row>
     <row r="447" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A447" t="inlineStr">
+      <c r="A447" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Global Sustainable Growth C Inc GBP</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr">
+      <c r="B447" s="6" t="inlineStr">
         <is>
           <t>GB00B68FGC22</t>
         </is>
@@ -8002,12 +8002,12 @@
       </c>
     </row>
     <row r="448" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A448" t="inlineStr">
+      <c r="A448" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Global Sustainable Optimum Income B Inc GBP</t>
         </is>
       </c>
-      <c r="B448" t="inlineStr">
+      <c r="B448" s="6" t="inlineStr">
         <is>
           <t>GB00BFZND546</t>
         </is>
@@ -8019,12 +8019,12 @@
       </c>
     </row>
     <row r="449" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A449" t="inlineStr">
+      <c r="A449" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Global Sustainable Optimum Income C Inc GBP</t>
         </is>
       </c>
-      <c r="B449" t="inlineStr">
+      <c r="B449" s="6" t="inlineStr">
         <is>
           <t>GB00BFZND652</t>
         </is>
@@ -8036,12 +8036,12 @@
       </c>
     </row>
     <row r="450" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A450" t="inlineStr">
+      <c r="A450" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Liberation IV C Acc GBP</t>
         </is>
       </c>
-      <c r="B450" t="inlineStr">
+      <c r="B450" s="6" t="inlineStr">
         <is>
           <t>GB00B5N42Z23</t>
         </is>
@@ -8053,12 +8053,12 @@
       </c>
     </row>
     <row r="451" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A451" t="inlineStr">
+      <c r="A451" s="6" t="inlineStr">
         <is>
           <t>Premier Miton Liberation IV C Inc GBP</t>
         </is>
       </c>
-      <c r="B451" t="inlineStr">
+      <c r="B451" s="6" t="inlineStr">
         <is>
           <t>GB00B55VCJ57</t>
         </is>
@@ -8070,12 +8070,12 @@
       </c>
     </row>
     <row r="452" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A452" t="inlineStr">
+      <c r="A452" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Asian Convertible Bond C NAV GBP</t>
         </is>
       </c>
-      <c r="B452" t="inlineStr">
+      <c r="B452" s="6" t="inlineStr">
         <is>
           <t>LU0451393879</t>
         </is>
@@ -8087,12 +8087,12 @@
       </c>
     </row>
     <row r="453" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A453" t="inlineStr">
+      <c r="A453" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Asian Opportunities C</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr">
+      <c r="B453" s="6" t="inlineStr">
         <is>
           <t>LU2280550695</t>
         </is>
@@ -8104,12 +8104,12 @@
       </c>
     </row>
     <row r="454" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A454" t="inlineStr">
+      <c r="A454" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Asian Total Return C Dis NAV GBP AV</t>
         </is>
       </c>
-      <c r="B454" t="inlineStr">
+      <c r="B454" s="6" t="inlineStr">
         <is>
           <t>LU0378802051</t>
         </is>
@@ -8121,12 +8121,12 @@
       </c>
     </row>
     <row r="455" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A455" t="inlineStr">
+      <c r="A455" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF BlueOrchard Emerging Markets Climate Bond C Acc GBP</t>
         </is>
       </c>
-      <c r="B455" t="inlineStr">
+      <c r="B455" s="6" t="inlineStr">
         <is>
           <t>LU2399671168</t>
         </is>
@@ -8138,12 +8138,12 @@
       </c>
     </row>
     <row r="456" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A456" t="inlineStr">
+      <c r="A456" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF EURO Corporate Bond A Acc NAV EUR</t>
         </is>
       </c>
-      <c r="B456" t="inlineStr">
+      <c r="B456" s="6" t="inlineStr">
         <is>
           <t>LU0113257694</t>
         </is>
@@ -8155,12 +8155,12 @@
       </c>
     </row>
     <row r="457" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A457" t="inlineStr">
+      <c r="A457" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF EURO Corporate Bond C Acc NAV EUR</t>
         </is>
       </c>
-      <c r="B457" t="inlineStr">
+      <c r="B457" s="6" t="inlineStr">
         <is>
           <t>LU0113258742</t>
         </is>
@@ -8172,12 +8172,12 @@
       </c>
     </row>
     <row r="458" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A458" t="inlineStr">
+      <c r="A458" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF EURO Corporate Bond C Dis NAV EUR AV</t>
         </is>
       </c>
-      <c r="B458" t="inlineStr">
+      <c r="B458" s="6" t="inlineStr">
         <is>
           <t>LU0552054859</t>
         </is>
@@ -8189,12 +8189,12 @@
       </c>
     </row>
     <row r="459" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A459" t="inlineStr">
+      <c r="A459" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF EURO Corporate Bond C Hedged Dis GBP NAV QF</t>
         </is>
       </c>
-      <c r="B459" t="inlineStr">
+      <c r="B459" s="6" t="inlineStr">
         <is>
           <t>LU1326303051</t>
         </is>
@@ -8206,12 +8206,12 @@
       </c>
     </row>
     <row r="460" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A460" t="inlineStr">
+      <c r="A460" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Emerging Markets Debt Total Return C Hedged Dis NAV GBP AV</t>
         </is>
       </c>
-      <c r="B460" t="inlineStr">
+      <c r="B460" s="6" t="inlineStr">
         <is>
           <t>LU0218201134</t>
         </is>
@@ -8223,12 +8223,12 @@
       </c>
     </row>
     <row r="461" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A461" t="inlineStr">
+      <c r="A461" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Emerging Markets Debt Total Return Z Hedged Dis NAV GBP AV</t>
         </is>
       </c>
-      <c r="B461" t="inlineStr">
+      <c r="B461" s="6" t="inlineStr">
         <is>
           <t>LU0968426865</t>
         </is>
@@ -8240,12 +8240,12 @@
       </c>
     </row>
     <row r="462" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A462" t="inlineStr">
+      <c r="A462" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF European Dividend Maximiser C DisNV</t>
         </is>
       </c>
-      <c r="B462" t="inlineStr">
+      <c r="B462" s="6" t="inlineStr">
         <is>
           <t>LU0321373267</t>
         </is>
@@ -8257,12 +8257,12 @@
       </c>
     </row>
     <row r="463" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A463" t="inlineStr">
+      <c r="A463" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF European Sustainable Equity C Dis GBP</t>
         </is>
       </c>
-      <c r="B463" t="inlineStr">
+      <c r="B463" s="6" t="inlineStr">
         <is>
           <t>LU2293689829</t>
         </is>
@@ -8274,12 +8274,12 @@
       </c>
     </row>
     <row r="464" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A464" t="inlineStr">
+      <c r="A464" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Frontier Markets Equity C Acc Nav GBP</t>
         </is>
       </c>
-      <c r="B464" t="inlineStr">
+      <c r="B464" s="6" t="inlineStr">
         <is>
           <t>LU0971766711</t>
         </is>
@@ -8291,12 +8291,12 @@
       </c>
     </row>
     <row r="465" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A465" t="inlineStr">
+      <c r="A465" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Bond C Acc Nav GBP</t>
         </is>
       </c>
-      <c r="B465" t="inlineStr">
+      <c r="B465" s="6" t="inlineStr">
         <is>
           <t>LU1509907181</t>
         </is>
@@ -8308,12 +8308,12 @@
       </c>
     </row>
     <row r="466" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A466" t="inlineStr">
+      <c r="A466" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Convertible Bond C Acc NAV GBP</t>
         </is>
       </c>
-      <c r="B466" t="inlineStr">
+      <c r="B466" s="6" t="inlineStr">
         <is>
           <t>LU0451393952</t>
         </is>
@@ -8325,12 +8325,12 @@
       </c>
     </row>
     <row r="467" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A467" t="inlineStr">
+      <c r="A467" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Convertible Bond C Dis NAV GBP AV</t>
         </is>
       </c>
-      <c r="B467" t="inlineStr">
+      <c r="B467" s="6" t="inlineStr">
         <is>
           <t>LU0458180394</t>
         </is>
@@ -8342,12 +8342,12 @@
       </c>
     </row>
     <row r="468" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A468" t="inlineStr">
+      <c r="A468" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Corporate Bond C Acc NAV EUR</t>
         </is>
       </c>
-      <c r="B468" t="inlineStr">
+      <c r="B468" s="6" t="inlineStr">
         <is>
           <t>LU0713761251</t>
         </is>
@@ -8359,12 +8359,12 @@
       </c>
     </row>
     <row r="469" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A469" t="inlineStr">
+      <c r="A469" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Credit Income C Hedged Inc NAV GBP</t>
         </is>
       </c>
-      <c r="B469" t="inlineStr">
+      <c r="B469" s="6" t="inlineStr">
         <is>
           <t>LU1514168613</t>
         </is>
@@ -8376,12 +8376,12 @@
       </c>
     </row>
     <row r="470" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A470" t="inlineStr">
+      <c r="A470" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Dividend Maximiser C NAV GBP</t>
         </is>
       </c>
-      <c r="B470" t="inlineStr">
+      <c r="B470" s="6" t="inlineStr">
         <is>
           <t>LU0339281494</t>
         </is>
@@ -8393,12 +8393,12 @@
       </c>
     </row>
     <row r="471" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A471" t="inlineStr">
+      <c r="A471" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Dividend Maximiser Z Dis NAV GBP QF</t>
         </is>
       </c>
-      <c r="B471" t="inlineStr">
+      <c r="B471" s="6" t="inlineStr">
         <is>
           <t>LU0966866922</t>
         </is>
@@ -8410,12 +8410,12 @@
       </c>
     </row>
     <row r="472" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A472" t="inlineStr">
+      <c r="A472" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Energy C Dis NAV GBP AV</t>
         </is>
       </c>
-      <c r="B472" t="inlineStr">
+      <c r="B472" s="6" t="inlineStr">
         <is>
           <t>LU0355356832</t>
         </is>
@@ -8427,12 +8427,12 @@
       </c>
     </row>
     <row r="473" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A473" t="inlineStr">
+      <c r="A473" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Energy Z Dis NAV GBP AV</t>
         </is>
       </c>
-      <c r="B473" t="inlineStr">
+      <c r="B473" s="6" t="inlineStr">
         <is>
           <t>LU0969110765</t>
         </is>
@@ -8444,12 +8444,12 @@
       </c>
     </row>
     <row r="474" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A474" t="inlineStr">
+      <c r="A474" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Equity Alpha C Dis NAV USD AV</t>
         </is>
       </c>
-      <c r="B474" t="inlineStr">
+      <c r="B474" s="6" t="inlineStr">
         <is>
           <t>LU0231327700</t>
         </is>
@@ -8461,12 +8461,12 @@
       </c>
     </row>
     <row r="475" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A475" t="inlineStr">
+      <c r="A475" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Equity Yield C Dis NAV USD</t>
         </is>
       </c>
-      <c r="B475" t="inlineStr">
+      <c r="B475" s="6" t="inlineStr">
         <is>
           <t>LU0225771319</t>
         </is>
@@ -8478,12 +8478,12 @@
       </c>
     </row>
     <row r="476" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A476" t="inlineStr">
+      <c r="A476" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Gold C Hedged Dis NAV GBP AV</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr">
+      <c r="B476" s="6" t="inlineStr">
         <is>
           <t>LU1223083590</t>
         </is>
@@ -8495,12 +8495,12 @@
       </c>
     </row>
     <row r="477" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A477" t="inlineStr">
+      <c r="A477" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global High Yield C Dis NAV GBP QV</t>
         </is>
       </c>
-      <c r="B477" t="inlineStr">
+      <c r="B477" s="6" t="inlineStr">
         <is>
           <t>LU0441868451</t>
         </is>
@@ -8512,12 +8512,12 @@
       </c>
     </row>
     <row r="478" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A478" t="inlineStr">
+      <c r="A478" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Inflation Linked Bond C Acc NAV EUR</t>
         </is>
       </c>
-      <c r="B478" t="inlineStr">
+      <c r="B478" s="6" t="inlineStr">
         <is>
           <t>LU0180781394</t>
         </is>
@@ -8529,12 +8529,12 @@
       </c>
     </row>
     <row r="479" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A479" t="inlineStr">
+      <c r="A479" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Inflation Linked Bond C Dis NAV GBP AV</t>
         </is>
       </c>
-      <c r="B479" t="inlineStr">
+      <c r="B479" s="6" t="inlineStr">
         <is>
           <t>LU0488034827</t>
         </is>
@@ -8546,12 +8546,12 @@
       </c>
     </row>
     <row r="480" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A480" t="inlineStr">
+      <c r="A480" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Inflation Linked Bond C Hedged Dis NAV GBP AV</t>
         </is>
       </c>
-      <c r="B480" t="inlineStr">
+      <c r="B480" s="6" t="inlineStr">
         <is>
           <t>LU0294151377</t>
         </is>
@@ -8563,12 +8563,12 @@
       </c>
     </row>
     <row r="481" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A481" t="inlineStr">
+      <c r="A481" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Innovation C Acc GBP</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr">
+      <c r="B481" s="6" t="inlineStr">
         <is>
           <t>LU2049716330</t>
         </is>
@@ -8580,12 +8580,12 @@
       </c>
     </row>
     <row r="482" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A482" t="inlineStr">
+      <c r="A482" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Multi Asset Balanced E Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B482" t="inlineStr">
+      <c r="B482" s="6" t="inlineStr">
         <is>
           <t>LU2996705385</t>
         </is>
@@ -8597,12 +8597,12 @@
       </c>
     </row>
     <row r="483" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A483" t="inlineStr">
+      <c r="A483" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Recovery C Acc Nav GBP</t>
         </is>
       </c>
-      <c r="B483" t="inlineStr">
+      <c r="B483" s="6" t="inlineStr">
         <is>
           <t>LU1108799971</t>
         </is>
@@ -8614,12 +8614,12 @@
       </c>
     </row>
     <row r="484" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A484" t="inlineStr">
+      <c r="A484" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Recovery C Hedged Acc Nav GBP</t>
         </is>
       </c>
-      <c r="B484" t="inlineStr">
+      <c r="B484" s="6" t="inlineStr">
         <is>
           <t>LU0956908742</t>
         </is>
@@ -8631,12 +8631,12 @@
       </c>
     </row>
     <row r="485" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A485" t="inlineStr">
+      <c r="A485" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Global Sustainable Food and Water C Inc GBP</t>
         </is>
       </c>
-      <c r="B485" t="inlineStr">
+      <c r="B485" s="6" t="inlineStr">
         <is>
           <t>LU2380234083</t>
         </is>
@@ -8648,12 +8648,12 @@
       </c>
     </row>
     <row r="486" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A486" t="inlineStr">
+      <c r="A486" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Greater China C Dis NAV GBP AV</t>
         </is>
       </c>
-      <c r="B486" t="inlineStr">
+      <c r="B486" s="6" t="inlineStr">
         <is>
           <t>LU0492969166</t>
         </is>
@@ -8665,12 +8665,12 @@
       </c>
     </row>
     <row r="487" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A487" t="inlineStr">
+      <c r="A487" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Latin American A Dis NAV GBP AV</t>
         </is>
       </c>
-      <c r="B487" t="inlineStr">
+      <c r="B487" s="6" t="inlineStr">
         <is>
           <t>LU0242619483</t>
         </is>
@@ -8682,12 +8682,12 @@
       </c>
     </row>
     <row r="488" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A488" t="inlineStr">
+      <c r="A488" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Securitised Credit C Hedged Acc NAV GBP</t>
         </is>
       </c>
-      <c r="B488" t="inlineStr">
+      <c r="B488" s="6" t="inlineStr">
         <is>
           <t>LU1662756284</t>
         </is>
@@ -8699,12 +8699,12 @@
       </c>
     </row>
     <row r="489" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A489" t="inlineStr">
+      <c r="A489" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Strategic Bond C Hedged Acc NAV GBP</t>
         </is>
       </c>
-      <c r="B489" t="inlineStr">
+      <c r="B489" s="6" t="inlineStr">
         <is>
           <t>LU0223051235</t>
         </is>
@@ -8716,12 +8716,12 @@
       </c>
     </row>
     <row r="490" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A490" t="inlineStr">
+      <c r="A490" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Strategic Credit C Acc NAV GBP</t>
         </is>
       </c>
-      <c r="B490" t="inlineStr">
+      <c r="B490" s="6" t="inlineStr">
         <is>
           <t>LU0995124079</t>
         </is>
@@ -8733,12 +8733,12 @@
       </c>
     </row>
     <row r="491" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A491" t="inlineStr">
+      <c r="A491" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF Sustainable Asian Equity A Acc GBP</t>
         </is>
       </c>
-      <c r="B491" t="inlineStr">
+      <c r="B491" s="6" t="inlineStr">
         <is>
           <t>LU2484002345</t>
         </is>
@@ -8750,12 +8750,12 @@
       </c>
     </row>
     <row r="492" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A492" t="inlineStr">
+      <c r="A492" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF UK Equity C Acc NAV GBP</t>
         </is>
       </c>
-      <c r="B492" t="inlineStr">
+      <c r="B492" s="6" t="inlineStr">
         <is>
           <t>LU0106246225</t>
         </is>
@@ -8767,12 +8767,12 @@
       </c>
     </row>
     <row r="493" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A493" t="inlineStr">
+      <c r="A493" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF UK Equity C Dis NAV GBP AV</t>
         </is>
       </c>
-      <c r="B493" t="inlineStr">
+      <c r="B493" s="6" t="inlineStr">
         <is>
           <t>LU0062906044</t>
         </is>
@@ -8784,12 +8784,12 @@
       </c>
     </row>
     <row r="494" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A494" t="inlineStr">
+      <c r="A494" s="6" t="inlineStr">
         <is>
           <t>Schroder ISF US Large Cap C GBP</t>
         </is>
       </c>
-      <c r="B494" t="inlineStr">
+      <c r="B494" s="6" t="inlineStr">
         <is>
           <t>LU2264145413</t>
         </is>
@@ -8801,12 +8801,12 @@
       </c>
     </row>
     <row r="495" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A495" t="inlineStr">
+      <c r="A495" s="6" t="inlineStr">
         <is>
           <t>Schroder Islamic Global Equity Z Z</t>
         </is>
       </c>
-      <c r="B495" t="inlineStr">
+      <c r="B495" s="6" t="inlineStr">
         <is>
           <t>GB00BF780Y53</t>
         </is>
@@ -8818,12 +8818,12 @@
       </c>
     </row>
     <row r="496" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A496" t="inlineStr">
+      <c r="A496" s="6" t="inlineStr">
         <is>
           <t>Schroder Long Dated Corporate Bond I Acc</t>
         </is>
       </c>
-      <c r="B496" t="inlineStr">
+      <c r="B496" s="6" t="inlineStr">
         <is>
           <t>GB0009569327</t>
         </is>
@@ -8835,12 +8835,12 @@
       </c>
     </row>
     <row r="497" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A497" t="inlineStr">
+      <c r="A497" s="6" t="inlineStr">
         <is>
           <t>Schroder MM Diversity Z Acc</t>
         </is>
       </c>
-      <c r="B497" t="inlineStr">
+      <c r="B497" s="6" t="inlineStr">
         <is>
           <t>GB00B60CZD52</t>
         </is>
@@ -8852,12 +8852,12 @@
       </c>
     </row>
     <row r="498" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A498" t="inlineStr">
+      <c r="A498" s="6" t="inlineStr">
         <is>
           <t>Schroder Managed Balanced I Acc</t>
         </is>
       </c>
-      <c r="B498" t="inlineStr">
+      <c r="B498" s="6" t="inlineStr">
         <is>
           <t>GB0002899846</t>
         </is>
@@ -8869,12 +8869,12 @@
       </c>
     </row>
     <row r="499" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A499" t="inlineStr">
+      <c r="A499" s="6" t="inlineStr">
         <is>
           <t>Schroder Managed Balanced I Inc</t>
         </is>
       </c>
-      <c r="B499" t="inlineStr">
+      <c r="B499" s="6" t="inlineStr">
         <is>
           <t>GB0002900388</t>
         </is>
@@ -8886,12 +8886,12 @@
       </c>
     </row>
     <row r="500" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A500" t="inlineStr">
+      <c r="A500" s="6" t="inlineStr">
         <is>
           <t>Schroder Managed Wealth Portfolio Z Acc</t>
         </is>
       </c>
-      <c r="B500" t="inlineStr">
+      <c r="B500" s="6" t="inlineStr">
         <is>
           <t>GB00B84YNB54</t>
         </is>
@@ -8903,12 +8903,12 @@
       </c>
     </row>
     <row r="501" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A501" t="inlineStr">
+      <c r="A501" s="6" t="inlineStr">
         <is>
           <t>Schroder Managed Wealth Portfolio Z Inc</t>
         </is>
       </c>
-      <c r="B501" t="inlineStr">
+      <c r="B501" s="6" t="inlineStr">
         <is>
           <t>GB00B7134X76</t>
         </is>
@@ -8920,12 +8920,12 @@
       </c>
     </row>
     <row r="502" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A502" t="inlineStr">
+      <c r="A502" s="6" t="inlineStr">
         <is>
           <t>UBAM Biodiversity Restoration KC GBP</t>
         </is>
       </c>
-      <c r="B502" t="inlineStr">
+      <c r="B502" s="6" t="inlineStr">
         <is>
           <t>LU2351028977</t>
         </is>
@@ -8937,12 +8937,12 @@
       </c>
     </row>
     <row r="503" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A503" t="inlineStr">
+      <c r="A503" s="6" t="inlineStr">
         <is>
           <t>UBAM Global High Yield Solution IHC GBP</t>
         </is>
       </c>
-      <c r="B503" t="inlineStr">
+      <c r="B503" s="6" t="inlineStr">
         <is>
           <t>LU0782386667</t>
         </is>
@@ -8954,12 +8954,12 @@
       </c>
     </row>
     <row r="504" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A504" t="inlineStr">
+      <c r="A504" s="6" t="inlineStr">
         <is>
           <t>UBAM Global High Yield Solution IHD GBP</t>
         </is>
       </c>
-      <c r="B504" t="inlineStr">
+      <c r="B504" s="6" t="inlineStr">
         <is>
           <t>LU0569864217</t>
         </is>
@@ -8971,12 +8971,12 @@
       </c>
     </row>
     <row r="505" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A505" t="inlineStr">
+      <c r="A505" s="6" t="inlineStr">
         <is>
           <t>UBAM Positive Impact Emerging Equity KC GBP</t>
         </is>
       </c>
-      <c r="B505" t="inlineStr">
+      <c r="B505" s="6" t="inlineStr">
         <is>
           <t>LU2051765191</t>
         </is>
@@ -8988,12 +8988,12 @@
       </c>
     </row>
     <row r="506" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A506" t="inlineStr">
+      <c r="A506" s="6" t="inlineStr">
         <is>
           <t>UBAM Positive Impact Emerging Equity KD GBP</t>
         </is>
       </c>
-      <c r="B506" t="inlineStr">
+      <c r="B506" s="6" t="inlineStr">
         <is>
           <t>LU2051765274</t>
         </is>
@@ -9005,12 +9005,12 @@
       </c>
     </row>
     <row r="507" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A507" t="inlineStr">
+      <c r="A507" s="6" t="inlineStr">
         <is>
           <t>UBS FTSE RAFI Developed 1000 Index C Acc</t>
         </is>
       </c>
-      <c r="B507" t="inlineStr">
+      <c r="B507" s="6" t="inlineStr">
         <is>
           <t>GB00BX9C1L56</t>
         </is>
@@ -9022,12 +9022,12 @@
       </c>
     </row>
     <row r="508" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A508" t="inlineStr">
+      <c r="A508" s="6" t="inlineStr">
         <is>
           <t>UBS FTSE RAFI Developed 1000 Index J Inc</t>
         </is>
       </c>
-      <c r="B508" t="inlineStr">
+      <c r="B508" s="6" t="inlineStr">
         <is>
           <t>GB00BYNNWN07</t>
         </is>
@@ -9039,12 +9039,12 @@
       </c>
     </row>
     <row r="509" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A509" t="inlineStr">
+      <c r="A509" s="6" t="inlineStr">
         <is>
           <t>UBS Global Allocation UK C Acc</t>
         </is>
       </c>
-      <c r="B509" t="inlineStr">
+      <c r="B509" s="6" t="inlineStr">
         <is>
           <t>GB00B4MGDQ07</t>
         </is>
@@ -9056,12 +9056,12 @@
       </c>
     </row>
     <row r="510" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A510" t="inlineStr">
+      <c r="A510" s="6" t="inlineStr">
         <is>
           <t>UBS Global Emerging Markets Equity C Acc</t>
         </is>
       </c>
-      <c r="B510" t="inlineStr">
+      <c r="B510" s="6" t="inlineStr">
         <is>
           <t>GB00B7L34154</t>
         </is>
@@ -9073,12 +9073,12 @@
       </c>
     </row>
     <row r="511" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A511" t="inlineStr">
+      <c r="A511" s="6" t="inlineStr">
         <is>
           <t>UBS Global Enhanced Equity Income C Acc</t>
         </is>
       </c>
-      <c r="B511" t="inlineStr">
+      <c r="B511" s="6" t="inlineStr">
         <is>
           <t>GB00BL0RSN63</t>
         </is>
@@ -9090,12 +9090,12 @@
       </c>
     </row>
     <row r="512" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A512" t="inlineStr">
+      <c r="A512" s="6" t="inlineStr">
         <is>
           <t>UBS Global Enhanced Equity Income C Inc</t>
         </is>
       </c>
-      <c r="B512" t="inlineStr">
+      <c r="B512" s="6" t="inlineStr">
         <is>
           <t>GB00BL0RSP87</t>
         </is>
@@ -9107,12 +9107,12 @@
       </c>
     </row>
     <row r="513" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A513" t="inlineStr">
+      <c r="A513" s="6" t="inlineStr">
         <is>
           <t>UBS LuxEqSCVLgTrmTh$ hQ A</t>
         </is>
       </c>
-      <c r="B513" t="inlineStr">
+      <c r="B513" s="6" t="inlineStr">
         <is>
           <t>LU1340049755</t>
         </is>
@@ -9124,12 +9124,12 @@
       </c>
     </row>
     <row r="514" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A514" t="inlineStr">
+      <c r="A514" s="6" t="inlineStr">
         <is>
           <t>UBS MSCI World Minimum Volatility Index C Acc</t>
         </is>
       </c>
-      <c r="B514" t="inlineStr">
+      <c r="B514" s="6" t="inlineStr">
         <is>
           <t>GB00BX9C1N70</t>
         </is>
@@ -9141,12 +9141,12 @@
       </c>
     </row>
     <row r="515" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A515" t="inlineStr">
+      <c r="A515" s="6" t="inlineStr">
         <is>
           <t>UBS MSCI World Minimum Volatility Index C Inc GBP</t>
         </is>
       </c>
-      <c r="B515" t="inlineStr">
+      <c r="B515" s="6" t="inlineStr">
         <is>
           <t>GB00BX9C1Q02</t>
         </is>
@@ -9158,12 +9158,12 @@
       </c>
     </row>
     <row r="516" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A516" t="inlineStr">
+      <c r="A516" s="6" t="inlineStr">
         <is>
           <t>UBS S&amp;P 500 Index C Acc</t>
         </is>
       </c>
-      <c r="B516" t="inlineStr">
+      <c r="B516" s="6" t="inlineStr">
         <is>
           <t>GB00BMN91T34</t>
         </is>
@@ -9175,12 +9175,12 @@
       </c>
     </row>
     <row r="517" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A517" t="inlineStr">
+      <c r="A517" s="6" t="inlineStr">
         <is>
           <t>UBS S&amp;P 500 Index C Inc</t>
         </is>
       </c>
-      <c r="B517" t="inlineStr">
+      <c r="B517" s="6" t="inlineStr">
         <is>
           <t>GB00BMN91V55</t>
         </is>
@@ -9192,12 +9192,12 @@
       </c>
     </row>
     <row r="518" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A518" t="inlineStr">
+      <c r="A518" s="6" t="inlineStr">
         <is>
           <t>UBS Sterling Corporate Bond Indexed C Grs Acc</t>
         </is>
       </c>
-      <c r="B518" t="inlineStr">
+      <c r="B518" s="6" t="inlineStr">
         <is>
           <t>GB00B95J1785</t>
         </is>
@@ -9209,12 +9209,12 @@
       </c>
     </row>
     <row r="519" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A519" t="inlineStr">
+      <c r="A519" s="6" t="inlineStr">
         <is>
           <t>UBS Sterling Corporate Bond Indexed C Grs Inc</t>
         </is>
       </c>
-      <c r="B519" t="inlineStr">
+      <c r="B519" s="6" t="inlineStr">
         <is>
           <t>GB00B9LD6X50</t>
         </is>
@@ -9226,12 +9226,12 @@
       </c>
     </row>
     <row r="520" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A520" t="inlineStr">
+      <c r="A520" s="6" t="inlineStr">
         <is>
           <t>UBS UK Equity Income C Acc</t>
         </is>
       </c>
-      <c r="B520" t="inlineStr">
+      <c r="B520" s="6" t="inlineStr">
         <is>
           <t>GB00B4W58959</t>
         </is>
@@ -9243,12 +9243,12 @@
       </c>
     </row>
     <row r="521" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A521" t="inlineStr">
+      <c r="A521" s="6" t="inlineStr">
         <is>
           <t>UBS UK Equity Income C Inc</t>
         </is>
       </c>
-      <c r="B521" t="inlineStr">
+      <c r="B521" s="6" t="inlineStr">
         <is>
           <t>GB00B8034464</t>
         </is>
@@ -9260,12 +9260,12 @@
       </c>
     </row>
     <row r="522" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A522" t="inlineStr">
+      <c r="A522" s="6" t="inlineStr">
         <is>
           <t>UBS US Equity Value C Acc</t>
         </is>
       </c>
-      <c r="B522" t="inlineStr">
+      <c r="B522" s="6" t="inlineStr">
         <is>
           <t>GB00B7V68L26</t>
         </is>
@@ -9277,12 +9277,12 @@
       </c>
     </row>
     <row r="523" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A523" t="inlineStr">
+      <c r="A523" s="6" t="inlineStr">
         <is>
           <t>UBS US Growth C Acc</t>
         </is>
       </c>
-      <c r="B523" t="inlineStr">
+      <c r="B523" s="6" t="inlineStr">
         <is>
           <t>GB00B7VHZX64</t>
         </is>
@@ -9294,12 +9294,12 @@
       </c>
     </row>
     <row r="524" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A524" t="inlineStr">
+      <c r="A524" s="6" t="inlineStr">
         <is>
           <t>UTI India Dynamic Equity RDR II Acc GBP</t>
         </is>
       </c>
-      <c r="B524" t="inlineStr">
+      <c r="B524" s="6" t="inlineStr">
         <is>
           <t>IE00BK1M2F34</t>
         </is>
@@ -9311,12 +9311,12 @@
       </c>
     </row>
     <row r="525" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A525" t="inlineStr">
+      <c r="A525" s="6" t="inlineStr">
         <is>
           <t>Unicorn Mastertrust B</t>
         </is>
       </c>
-      <c r="B525" t="inlineStr">
+      <c r="B525" s="6" t="inlineStr">
         <is>
           <t>GB0031218018</t>
         </is>
@@ -9328,12 +9328,12 @@
       </c>
     </row>
     <row r="526" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A526" t="inlineStr">
+      <c r="A526" s="6" t="inlineStr">
         <is>
           <t>Unicorn Outstanding British Companies B</t>
         </is>
       </c>
-      <c r="B526" t="inlineStr">
+      <c r="B526" s="6" t="inlineStr">
         <is>
           <t>GB00B1GGDH66</t>
         </is>
@@ -9345,12 +9345,12 @@
       </c>
     </row>
     <row r="527" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A527" t="inlineStr">
+      <c r="A527" s="6" t="inlineStr">
         <is>
           <t>Unicorn UK Ethical Income B Acc</t>
         </is>
       </c>
-      <c r="B527" t="inlineStr">
+      <c r="B527" s="6" t="inlineStr">
         <is>
           <t>GB00BYQCS257</t>
         </is>
@@ -9362,12 +9362,12 @@
       </c>
     </row>
     <row r="528" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A528" t="inlineStr">
+      <c r="A528" s="6" t="inlineStr">
         <is>
           <t>Unicorn UK Ethical Income B Inc</t>
         </is>
       </c>
-      <c r="B528" t="inlineStr">
+      <c r="B528" s="6" t="inlineStr">
         <is>
           <t>GB00BYP2Y515</t>
         </is>
@@ -9379,12 +9379,12 @@
       </c>
     </row>
     <row r="529" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A529" t="inlineStr">
+      <c r="A529" s="6" t="inlineStr">
         <is>
           <t>Unicorn UK Growth B Inc</t>
         </is>
       </c>
-      <c r="B529" t="inlineStr">
+      <c r="B529" s="6" t="inlineStr">
         <is>
           <t>GB0031217937</t>
         </is>
@@ -9396,12 +9396,12 @@
       </c>
     </row>
     <row r="530" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A530" t="inlineStr">
+      <c r="A530" s="6" t="inlineStr">
         <is>
           <t>Unicorn UK Income B Acc</t>
         </is>
       </c>
-      <c r="B530" t="inlineStr">
+      <c r="B530" s="6" t="inlineStr">
         <is>
           <t>GB00B9XQFY62</t>
         </is>
@@ -9413,12 +9413,12 @@
       </c>
     </row>
     <row r="531" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A531" t="inlineStr">
+      <c r="A531" s="6" t="inlineStr">
         <is>
           <t>Unicorn UK Income B Inc</t>
         </is>
       </c>
-      <c r="B531" t="inlineStr">
+      <c r="B531" s="6" t="inlineStr">
         <is>
           <t>GB00B00Z1R87</t>
         </is>
@@ -9430,12 +9430,12 @@
       </c>
     </row>
     <row r="532" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A532" t="inlineStr">
+      <c r="A532" s="6" t="inlineStr">
         <is>
           <t>Unicorn UK Income C Inc</t>
         </is>
       </c>
-      <c r="B532" t="inlineStr">
+      <c r="B532" s="6" t="inlineStr">
         <is>
           <t>GB00BNKJ9Y43</t>
         </is>
@@ -9447,12 +9447,12 @@
       </c>
     </row>
     <row r="533" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A533" t="inlineStr">
+      <c r="A533" s="6" t="inlineStr">
         <is>
           <t>Unicorn UK Smaller Companies B Inc GBX</t>
         </is>
       </c>
-      <c r="B533" t="inlineStr">
+      <c r="B533" s="6" t="inlineStr">
         <is>
           <t>GB0031785065</t>
         </is>
@@ -9464,12 +9464,12 @@
       </c>
     </row>
     <row r="534" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A534" t="inlineStr">
+      <c r="A534" s="6" t="inlineStr">
         <is>
           <t>Unicorn UK Smaller Companies C Inc GBX</t>
         </is>
       </c>
-      <c r="B534" t="inlineStr">
+      <c r="B534" s="6" t="inlineStr">
         <is>
           <t>GB00BNG8KX15</t>
         </is>
@@ -9481,12 +9481,12 @@
       </c>
     </row>
     <row r="535" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A535" t="inlineStr">
+      <c r="A535" s="6" t="inlineStr">
         <is>
           <t>Vanguard ActiveLife Climate Aware 40-50% Equity A Acc GBP</t>
         </is>
       </c>
-      <c r="B535" t="inlineStr">
+      <c r="B535" s="6" t="inlineStr">
         <is>
           <t>GB00BMCQRZ38</t>
         </is>
@@ -9498,12 +9498,12 @@
       </c>
     </row>
     <row r="536" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A536" t="inlineStr">
+      <c r="A536" s="6" t="inlineStr">
         <is>
           <t>Vanguard ActiveLife Climate Aware 40-50% Equity A Inc GBP</t>
         </is>
       </c>
-      <c r="B536" t="inlineStr">
+      <c r="B536" s="6" t="inlineStr">
         <is>
           <t>GB00BMCQRX14</t>
         </is>
@@ -9515,12 +9515,12 @@
       </c>
     </row>
     <row r="537" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A537" t="inlineStr">
+      <c r="A537" s="6" t="inlineStr">
         <is>
           <t>Vanguard ActiveLife Climate Aware 60-70% Equity A Acc</t>
         </is>
       </c>
-      <c r="B537" t="inlineStr">
+      <c r="B537" s="6" t="inlineStr">
         <is>
           <t>GB00BZ830054</t>
         </is>
@@ -9532,12 +9532,12 @@
       </c>
     </row>
     <row r="538" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A538" t="inlineStr">
+      <c r="A538" s="6" t="inlineStr">
         <is>
           <t>Vanguard ActiveLife Climate Aware 60-70% Equity A Inc</t>
         </is>
       </c>
-      <c r="B538" t="inlineStr">
+      <c r="B538" s="6" t="inlineStr">
         <is>
           <t>GB00BZ82ZZ20</t>
         </is>
@@ -9549,12 +9549,12 @@
       </c>
     </row>
     <row r="539" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A539" t="inlineStr">
+      <c r="A539" s="6" t="inlineStr">
         <is>
           <t>Vanguard ActiveLife Climate Aware 80-90% Equity A Acc GBP</t>
         </is>
       </c>
-      <c r="B539" t="inlineStr">
+      <c r="B539" s="6" t="inlineStr">
         <is>
           <t>GB00BMCQS161</t>
         </is>
@@ -9566,12 +9566,12 @@
       </c>
     </row>
     <row r="540" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A540" t="inlineStr">
+      <c r="A540" s="6" t="inlineStr">
         <is>
           <t>Vanguard ActiveLife Climate Aware 80-90% Equity A Inc GBP</t>
         </is>
       </c>
-      <c r="B540" t="inlineStr">
+      <c r="B540" s="6" t="inlineStr">
         <is>
           <t>GB00BMCQS054</t>
         </is>
@@ -9583,12 +9583,12 @@
       </c>
     </row>
     <row r="541" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A541" t="inlineStr">
+      <c r="A541" s="6" t="inlineStr">
         <is>
           <t>Vanguard ESG Developed European Index Acc GBP</t>
         </is>
       </c>
-      <c r="B541" t="inlineStr">
+      <c r="B541" s="6" t="inlineStr">
         <is>
           <t>IE00B76VTL96</t>
         </is>
@@ -9600,12 +9600,12 @@
       </c>
     </row>
     <row r="542" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A542" t="inlineStr">
+      <c r="A542" s="6" t="inlineStr">
         <is>
           <t>Vanguard ESG Developed European Index Inc GBP</t>
         </is>
       </c>
-      <c r="B542" t="inlineStr">
+      <c r="B542" s="6" t="inlineStr">
         <is>
           <t>IE00B76VTR58</t>
         </is>
@@ -9617,12 +9617,12 @@
       </c>
     </row>
     <row r="543" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A543" t="inlineStr">
+      <c r="A543" s="6" t="inlineStr">
         <is>
           <t>Vanguard ESG Developed World All Cap Equity Index Acc GBP</t>
         </is>
       </c>
-      <c r="B543" t="inlineStr">
+      <c r="B543" s="6" t="inlineStr">
         <is>
           <t>IE00B76VTN11</t>
         </is>
@@ -9634,12 +9634,12 @@
       </c>
     </row>
     <row r="544" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A544" t="inlineStr">
+      <c r="A544" s="6" t="inlineStr">
         <is>
           <t>Vanguard ESG Developed World All Cap Equity Index Inc GBP</t>
         </is>
       </c>
-      <c r="B544" t="inlineStr">
+      <c r="B544" s="6" t="inlineStr">
         <is>
           <t>IE00B76VTM04</t>
         </is>
@@ -9651,12 +9651,12 @@
       </c>
     </row>
     <row r="545" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A545" t="inlineStr">
+      <c r="A545" s="6" t="inlineStr">
         <is>
           <t>Vanguard ESG Emerging Markets All Cap Equity Index Acc GBP</t>
         </is>
       </c>
-      <c r="B545" t="inlineStr">
+      <c r="B545" s="6" t="inlineStr">
         <is>
           <t>IE00BKV0VZ05</t>
         </is>
@@ -9668,12 +9668,12 @@
       </c>
     </row>
     <row r="546" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A546" t="inlineStr">
+      <c r="A546" s="6" t="inlineStr">
         <is>
           <t>Vanguard ESG Emerging Markets All Cap Equity Index Inc GBP</t>
         </is>
       </c>
-      <c r="B546" t="inlineStr">
+      <c r="B546" s="6" t="inlineStr">
         <is>
           <t>IE00BKV0W029</t>
         </is>
@@ -9685,12 +9685,12 @@
       </c>
     </row>
     <row r="547" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A547" t="inlineStr">
+      <c r="A547" s="6" t="inlineStr">
         <is>
           <t>Vanguard ESG Global Corporate Bond Index Hedged Acc GBP</t>
         </is>
       </c>
-      <c r="B547" t="inlineStr">
+      <c r="B547" s="6" t="inlineStr">
         <is>
           <t>IE00BNDS1195</t>
         </is>
@@ -9702,12 +9702,12 @@
       </c>
     </row>
     <row r="548" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A548" t="inlineStr">
+      <c r="A548" s="6" t="inlineStr">
         <is>
           <t>Vanguard Emerging Markets Bond Investor Acc EUR</t>
         </is>
       </c>
-      <c r="B548" t="inlineStr">
+      <c r="B548" s="6" t="inlineStr">
         <is>
           <t>IE00BKLWXS37</t>
         </is>
@@ -9719,12 +9719,12 @@
       </c>
     </row>
     <row r="549" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A549" t="inlineStr">
+      <c r="A549" s="6" t="inlineStr">
         <is>
           <t>Vanguard Emerging Markets Bond Investor Acc GBP</t>
         </is>
       </c>
-      <c r="B549" t="inlineStr">
+      <c r="B549" s="6" t="inlineStr">
         <is>
           <t>IE00BKLWXP06</t>
         </is>
@@ -9736,12 +9736,12 @@
       </c>
     </row>
     <row r="550" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A550" t="inlineStr">
+      <c r="A550" s="6" t="inlineStr">
         <is>
           <t>Vanguard Emerging Markets Stock Index Acc GBP</t>
         </is>
       </c>
-      <c r="B550" t="inlineStr">
+      <c r="B550" s="6" t="inlineStr">
         <is>
           <t>IE00B50MZ724</t>
         </is>
@@ -9753,12 +9753,12 @@
       </c>
     </row>
     <row r="551" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A551" t="inlineStr">
+      <c r="A551" s="6" t="inlineStr">
         <is>
           <t>Vanguard Emerging Markets Stock Index Inc GBP</t>
         </is>
       </c>
-      <c r="B551" t="inlineStr">
+      <c r="B551" s="6" t="inlineStr">
         <is>
           <t>IE00B51KVT96</t>
         </is>
@@ -9770,12 +9770,12 @@
       </c>
     </row>
     <row r="552" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A552" t="inlineStr">
+      <c r="A552" s="6" t="inlineStr">
         <is>
           <t>YFS Charteris Global Macro A Acc</t>
         </is>
       </c>
-      <c r="B552" t="inlineStr">
+      <c r="B552" s="6" t="inlineStr">
         <is>
           <t>GB00BV8VPH36</t>
         </is>
@@ -9787,12 +9787,12 @@
       </c>
     </row>
     <row r="553" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A553" t="inlineStr">
+      <c r="A553" s="6" t="inlineStr">
         <is>
           <t>YFS Charteris Gold and Precious Metals I Acc</t>
         </is>
       </c>
-      <c r="B553" t="inlineStr">
+      <c r="B553" s="6" t="inlineStr">
         <is>
           <t>GB00BYQ2JY43</t>
         </is>
@@ -9804,12 +9804,12 @@
       </c>
     </row>
     <row r="554" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A554" t="inlineStr">
+      <c r="A554" s="6" t="inlineStr">
         <is>
           <t>YFS Charteris Gold and Precious Metals I Inc</t>
         </is>
       </c>
-      <c r="B554" t="inlineStr">
+      <c r="B554" s="6" t="inlineStr">
         <is>
           <t>GB00BYQ2JZ59</t>
         </is>
@@ -9821,12 +9821,12 @@
       </c>
     </row>
     <row r="555" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A555" t="inlineStr">
+      <c r="A555" s="6" t="inlineStr">
         <is>
           <t>YFS Charteris Strategic Bond I Acc</t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
+      <c r="B555" s="6" t="inlineStr">
         <is>
           <t>GB00BD9GLM88</t>
         </is>
@@ -9838,12 +9838,12 @@
       </c>
     </row>
     <row r="556" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A556" t="inlineStr">
+      <c r="A556" s="6" t="inlineStr">
         <is>
           <t>YFS Charteris Strategic Bond I Inc</t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
+      <c r="B556" s="6" t="inlineStr">
         <is>
           <t>GB00BD9GLN95</t>
         </is>
@@ -9855,12 +9855,12 @@
       </c>
     </row>
     <row r="557" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A557" t="inlineStr">
+      <c r="A557" s="6" t="inlineStr">
         <is>
           <t>YFS Chawton Global Equity Income B Acc GBP</t>
         </is>
       </c>
-      <c r="B557" t="inlineStr">
+      <c r="B557" s="6" t="inlineStr">
         <is>
           <t>GB00BJ1GXX37</t>
         </is>
@@ -9872,12 +9872,12 @@
       </c>
     </row>
     <row r="558" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A558" t="inlineStr">
+      <c r="A558" s="6" t="inlineStr">
         <is>
           <t>YFS Chawton Global Equity Income B Inc GBP</t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
+      <c r="B558" s="6" t="inlineStr">
         <is>
           <t>GB00BJ1GY073</t>
         </is>
@@ -9889,12 +9889,12 @@
       </c>
     </row>
     <row r="559" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A559" t="inlineStr">
+      <c r="A559" s="6" t="inlineStr">
         <is>
           <t>YFS Kernow Equity Navigator A Acc GBP</t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
+      <c r="B559" s="6" t="inlineStr">
         <is>
           <t>GB00BPJGXQ09</t>
         </is>
@@ -9906,12 +9906,12 @@
       </c>
     </row>
     <row r="560" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A560" t="inlineStr">
+      <c r="A560" s="6" t="inlineStr">
         <is>
           <t>YFS Knox Total Return F Inc</t>
         </is>
       </c>
-      <c r="B560" t="inlineStr">
+      <c r="B560" s="6" t="inlineStr">
         <is>
           <t>GB00BYZZBM62</t>
         </is>
@@ -9923,12 +9923,12 @@
       </c>
     </row>
     <row r="561" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A561" t="inlineStr">
+      <c r="A561" s="6" t="inlineStr">
         <is>
           <t>YFS Whitman UK Small Cap Growth B Acc GBP</t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
+      <c r="B561" s="6" t="inlineStr">
         <is>
           <t>GB00BMTM5059</t>
         </is>
@@ -9940,12 +9940,12 @@
       </c>
     </row>
     <row r="562" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A562" t="inlineStr">
+      <c r="A562" s="6" t="inlineStr">
         <is>
           <t>YFS Whitman UK Small Cap Growth C Acc GBP</t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
+      <c r="B562" s="6" t="inlineStr">
         <is>
           <t>GB00BMTM5166</t>
         </is>
@@ -9957,12 +9957,12 @@
       </c>
     </row>
     <row r="563" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A563" t="inlineStr">
+      <c r="A563" s="6" t="inlineStr">
         <is>
           <t>YFS Whitman UK Small Cap Growth D Acc GBP</t>
         </is>
       </c>
-      <c r="B563" t="inlineStr">
+      <c r="B563" s="6" t="inlineStr">
         <is>
           <t>GB00BS55QN01</t>
         </is>
@@ -9974,12 +9974,12 @@
       </c>
     </row>
     <row r="564" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A564" t="inlineStr">
+      <c r="A564" s="6" t="inlineStr">
         <is>
           <t>Zadig Memnon European U2 GBP</t>
         </is>
       </c>
-      <c r="B564" t="inlineStr">
+      <c r="B564" s="6" t="inlineStr">
         <is>
           <t>LU0578134156</t>
         </is>

--- a/spreadsheet/charles_stanley.xlsx
+++ b/spreadsheet/charles_stanley.xlsx
@@ -435,21 +435,31 @@
           <t>https://www.charles-stanley-direct.co.uk/ViewFund?InvestmentId=G9%2BpUE7%2BaEg%3D&amp;Isin=GB00B2PB2C75&amp;PreviousSearchResults=%2FInvestmentSearch%2FSearch%3FSearchType%3DKeywordSearch%26Category%3DFunds%26SortColumn%3DName%26SortDirection%3DAsc%26Pagesize%3D50%26Page%3D1</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Invest in this fund within an ISA, JISA, SIPP or Investment Account</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>7IM AAP Adventurous C Inc</t>
+          <t>7IM Adventurous C Acc</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>GB00B2PB2B68</t>
+          <t>GB0033958009</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>https://www.charles-stanley-direct.co.uk/ViewFund?InvestmentId=YU2xRK6U3r0%3D&amp;Isin=GB00B2PB2B68&amp;PreviousSearchResults=%2FInvestmentSearch%2FSearch%3FSearchType%3DKeywordSearch%26Category%3DFunds%26SortColumn%3DName%26SortDirection%3DAsc%26Pagesize%3D50%26Page%3D1</t>
+          <t>https://www.charles-stanley-direct.co.uk/ViewFund?InvestmentId=geMXjfW4gYY%3D&amp;Isin=GB0033958009&amp;PreviousSearchResults=%2FInvestmentSearch%2FSearch%3FSearchType%3DKeywordSearch%26Category%3DFunds%26SortColumn%3DName%26SortDirection%3DAsc%26Pagesize%3D50%26Page%3D1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Invest in this fund within an ISA, JISA, SIPP or Investment Account</t>
         </is>
       </c>
     </row>
